--- a/reports/raw-views/assets/tables/micro_semantic_richness.xlsx
+++ b/reports/raw-views/assets/tables/micro_semantic_richness.xlsx
@@ -441,62 +441,62 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Autores</t>
+          <t>Authors</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Autores_color</t>
+          <t>Authors_color</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Autores_N</t>
+          <t>Authors_N</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Pares</t>
+          <t>Peers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Pares_color</t>
+          <t>Peers_color</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Pares_N</t>
+          <t>Peers_N</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Analistas</t>
+          <t>Analysts</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Analistas_color</t>
+          <t>Analysts_color</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Analistas_N</t>
+          <t>Analysts_N</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>IA_color</t>
+          <t>AI_color</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>IA_N</t>
+          <t>AI_N</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
         <v>0.7098832130432129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4465635716915131</v>
+        <v>0.4399627447128296</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -517,7 +517,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8617878556251526</v>
+        <v>0.8665327429771423</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -526,7 +526,7 @@
         <v>9.694444444444445</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6503101587295532</v>
+        <v>0.639947772026062</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -535,7 +535,7 @@
         <v>21.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6948258280754089</v>
+        <v>0.6937544941902161</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -552,7 +552,7 @@
         <v>0.6762779951095581</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7405539751052856</v>
+        <v>0.7755086421966553</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -561,7 +561,7 @@
         <v>19.375</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8512692451477051</v>
+        <v>0.8458156585693359</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6589226722717285</v>
+        <v>0.693230152130127</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -579,7 +579,7 @@
         <v>17.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6107354164123535</v>
+        <v>0.6348400115966797</v>
       </c>
       <c r="M3" t="n">
         <v>5</v>
@@ -596,7 +596,7 @@
         <v>0.6345182061195374</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7422360777854919</v>
+        <v>0.7554744482040405</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -605,7 +605,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5950314998626709</v>
+        <v>0.5899169445037842</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -614,7 +614,7 @@
         <v>2.555555555555555</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5745938420295715</v>
+        <v>0.5859652757644653</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -623,7 +623,7 @@
         <v>18.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4456367492675781</v>
+        <v>0.4022833108901978</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>0.6905345320701599</v>
+        <v>0.729841411113739</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -647,7 +647,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6866968274116516</v>
+        <v>0.7029569149017334</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -656,7 +656,7 @@
         <v>3.583333333333333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4850305914878845</v>
+        <v>0.5566564798355103</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -665,7 +665,7 @@
         <v>11.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4556073546409607</v>
+        <v>0.401788592338562</v>
       </c>
       <c r="M5" t="n">
         <v>5</v>
@@ -682,7 +682,7 @@
         <v>0.732783317565918</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9617677927017212</v>
+        <v>0.9477929472923279</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
@@ -691,7 +691,7 @@
         <v>8.75</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9999999403953552</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -700,7 +700,7 @@
         <v>11.80555555555556</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6941680312156677</v>
+        <v>0.6642497777938843</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -709,7 +709,7 @@
         <v>20</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5821338891983032</v>
+        <v>0.5312587022781372</v>
       </c>
       <c r="M6" t="n">
         <v>5</v>
@@ -726,7 +726,7 @@
         <v>0.759387195110321</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7299776077270508</v>
+        <v>0.7514709234237671</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -735,7 +735,7 @@
         <v>11.375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.846882700920105</v>
+        <v>0.8678907155990601</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
@@ -744,7 +744,7 @@
         <v>6.555555555555555</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6180099248886108</v>
+        <v>0.6198131442070007</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -753,7 +753,7 @@
         <v>20.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4682013392448425</v>
+        <v>0.4254969954490662</v>
       </c>
       <c r="M7" t="n">
         <v>5</v>
@@ -770,7 +770,7 @@
         <v>0.7021883130073547</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6724001169204712</v>
+        <v>0.6083551049232483</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -779,7 +779,7 @@
         <v>16.75</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7998970746994019</v>
+        <v>0.7953619956970215</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -788,7 +788,7 @@
         <v>13.30555555555556</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5363410711288452</v>
+        <v>0.5580720901489258</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -797,7 +797,7 @@
         <v>17.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5171021819114685</v>
+        <v>0.4779924154281616</v>
       </c>
       <c r="M8" t="n">
         <v>5</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0.5322105884552002</v>
+        <v>0.6243325471878052</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -821,7 +821,7 @@
         <v>3.75</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6150782108306885</v>
+        <v>0.6635497808456421</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
@@ -830,7 +830,7 @@
         <v>4.333333333333333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6272317171096802</v>
+        <v>0.6369573473930359</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -839,7 +839,7 @@
         <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4203052222728729</v>
+        <v>0.4210035800933838</v>
       </c>
       <c r="M9" t="n">
         <v>5</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0.7473574876785278</v>
+        <v>0.7218131422996521</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -863,7 +863,7 @@
         <v>6.625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8645196557044983</v>
+        <v>0.848808228969574</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -872,7 +872,7 @@
         <v>7.083333333333333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7095152139663696</v>
+        <v>0.7171789407730103</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
@@ -881,7 +881,7 @@
         <v>23.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5445066690444946</v>
+        <v>0.5097904801368713</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
@@ -905,7 +905,7 @@
         <v>2.75</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6626378297805786</v>
+        <v>0.6751291751861572</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -914,7 +914,7 @@
         <v>5.222222222222222</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5792490243911743</v>
+        <v>0.5681167244911194</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -923,7 +923,7 @@
         <v>9.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4700775742530823</v>
+        <v>0.4683035612106323</v>
       </c>
       <c r="M11" t="n">
         <v>5</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0.7596328258514404</v>
+        <v>0.789329469203949</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
@@ -947,7 +947,7 @@
         <v>10.75</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7909009456634521</v>
+        <v>0.8463919162750244</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
@@ -956,7 +956,7 @@
         <v>3.527777777777778</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6395813822746277</v>
+        <v>0.6304858326911926</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -965,7 +965,7 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3330167233943939</v>
+        <v>0.2821500897407532</v>
       </c>
       <c r="M12" t="n">
         <v>5</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.7299959659576416</v>
+        <v>0.6509974002838135</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
@@ -989,7 +989,7 @@
         <v>17.375</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8464430570602417</v>
+        <v>0.7755147218704224</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
@@ -998,7 +998,7 @@
         <v>8.694444444444445</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5419093370437622</v>
+        <v>0.5933381319046021</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
@@ -1007,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>0.572374701499939</v>
+        <v>0.573968231678009</v>
       </c>
       <c r="M13" t="n">
         <v>5</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.6533894538879395</v>
+        <v>0.648712158203125</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -1031,7 +1031,7 @@
         <v>13.25</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9306353330612183</v>
+        <v>0.9327827095985413</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
@@ -1040,7 +1040,7 @@
         <v>7.694444444444445</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6153032779693604</v>
+        <v>0.5974658131599426</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -1049,7 +1049,7 @@
         <v>19.75</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5184723138809204</v>
+        <v>0.4963589608669281</v>
       </c>
       <c r="M14" t="n">
         <v>5</v>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0.7214872241020203</v>
+        <v>0.7875330448150635</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
@@ -1073,7 +1073,7 @@
         <v>8.75</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8476237058639526</v>
+        <v>0.7602059841156006</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -1096,7 +1096,7 @@
         <v>0.7199677228927612</v>
       </c>
       <c r="C16" t="n">
-        <v>0.783109724521637</v>
+        <v>0.7687399387359619</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
@@ -1105,7 +1105,7 @@
         <v>10.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7218666076660156</v>
+        <v>0.8098189830780029</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -1114,7 +1114,7 @@
         <v>4.916666666666667</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7925670146942139</v>
+        <v>0.7904614210128784</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -1123,7 +1123,7 @@
         <v>11.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3591094315052032</v>
+        <v>0.3783270120620728</v>
       </c>
       <c r="M16" t="n">
         <v>5</v>
@@ -1140,7 +1140,7 @@
         <v>0.6476995348930359</v>
       </c>
       <c r="C17" t="n">
-        <v>0.654712438583374</v>
+        <v>0.6662125587463379</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
@@ -1149,7 +1149,7 @@
         <v>17.875</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8195036053657532</v>
+        <v>0.8322668075561523</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
@@ -1158,7 +1158,7 @@
         <v>10.55555555555556</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3730570673942566</v>
+        <v>0.4384181797504425</v>
       </c>
       <c r="J17" t="n">
         <v>3</v>
@@ -1167,7 +1167,7 @@
         <v>16.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3571753799915314</v>
+        <v>0.380978524684906</v>
       </c>
       <c r="M17" t="n">
         <v>5</v>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0.6354497671127319</v>
+        <v>0.6348052024841309</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1191,7 +1191,7 @@
         <v>5.375</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7220765352249146</v>
+        <v>0.7088180780410767</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
@@ -1200,7 +1200,7 @@
         <v>4.25</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3230847120285034</v>
+        <v>0.3434343636035919</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
@@ -1209,7 +1209,7 @@
         <v>10.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3842054605484009</v>
+        <v>0.3587056398391724</v>
       </c>
       <c r="M18" t="n">
         <v>5</v>
@@ -1226,7 +1226,7 @@
         <v>0.592768669128418</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5380998849868774</v>
+        <v>0.5887188911437988</v>
       </c>
       <c r="D19" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>6.625</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8040767908096313</v>
+        <v>0.7881573438644409</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
@@ -1244,7 +1244,7 @@
         <v>5.222222222222222</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8589310050010681</v>
+        <v>0.8652694821357727</v>
       </c>
       <c r="J19" t="n">
         <v>2</v>
@@ -1253,7 +1253,7 @@
         <v>5.75</v>
       </c>
       <c r="L19" t="n">
-        <v>0.345004141330719</v>
+        <v>0.3328981995582581</v>
       </c>
       <c r="M19" t="n">
         <v>5</v>
@@ -1270,7 +1270,7 @@
         <v>0.7475150227546692</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6482784748077393</v>
+        <v>0.6159375309944153</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
@@ -1279,7 +1279,7 @@
         <v>40.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7988125085830688</v>
+        <v>0.8188999891281128</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1288,7 +1288,7 @@
         <v>4.666666666666667</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7293371558189392</v>
+        <v>0.6926627159118652</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
@@ -1297,7 +1297,7 @@
         <v>19</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4212687611579895</v>
+        <v>0.3998068273067474</v>
       </c>
       <c r="M20" t="n">
         <v>5</v>
@@ -1314,7 +1314,7 @@
         <v>0.6530535817146301</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7504193782806396</v>
+        <v>0.7504833936691284</v>
       </c>
       <c r="D21" t="n">
         <v>3</v>
@@ -1323,7 +1323,7 @@
         <v>15.25</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6921337842941284</v>
+        <v>0.7211071848869324</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1332,7 +1332,7 @@
         <v>5.305555555555555</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3955633342266083</v>
+        <v>0.4250962436199188</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -1341,7 +1341,7 @@
         <v>15.25</v>
       </c>
       <c r="L21" t="n">
-        <v>0.274764209985733</v>
+        <v>0.2930305898189545</v>
       </c>
       <c r="M21" t="n">
         <v>5</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0.6561062335968018</v>
+        <v>0.622251570224762</v>
       </c>
       <c r="D22" t="n">
         <v>2</v>
@@ -1365,7 +1365,7 @@
         <v>8.875</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7661898136138916</v>
+        <v>0.7734487056732178</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -1374,7 +1374,7 @@
         <v>16.97222222222222</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4926313757896423</v>
+        <v>0.5077676177024841</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -1383,7 +1383,7 @@
         <v>16.5</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3923847377300262</v>
+        <v>0.382670521736145</v>
       </c>
       <c r="M22" t="n">
         <v>5</v>
@@ -1400,7 +1400,7 @@
         <v>0.7238247394561768</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8147828578948975</v>
+        <v>0.7372199296951294</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1409,7 +1409,7 @@
         <v>12.875</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8148183226585388</v>
+        <v>0.7917784452438354</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
@@ -1418,7 +1418,7 @@
         <v>8.75</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5639085173606873</v>
+        <v>0.6006447076797485</v>
       </c>
       <c r="J23" t="n">
         <v>2</v>
@@ -1427,7 +1427,7 @@
         <v>11.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0.4111796319484711</v>
+        <v>0.3894200026988983</v>
       </c>
       <c r="M23" t="n">
         <v>5</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0.7084392309188843</v>
+        <v>0.6138978004455566</v>
       </c>
       <c r="D24" t="n">
         <v>2</v>
@@ -1451,7 +1451,7 @@
         <v>12.5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6221619844436646</v>
+        <v>0.5657546520233154</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1460,7 +1460,7 @@
         <v>3.583333333333333</v>
       </c>
       <c r="I24" t="n">
-        <v>0.683545708656311</v>
+        <v>0.6209378242492676</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
@@ -1469,7 +1469,7 @@
         <v>10.25</v>
       </c>
       <c r="L24" t="n">
-        <v>0.4158812761306763</v>
+        <v>0.3990321755409241</v>
       </c>
       <c r="M24" t="n">
         <v>5</v>
@@ -1486,7 +1486,7 @@
         <v>0.7232909202575684</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7534863948822021</v>
+        <v>0.8085576295852661</v>
       </c>
       <c r="D25" t="n">
         <v>2</v>
@@ -1495,7 +1495,7 @@
         <v>9</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5797702074050903</v>
+        <v>0.5920165777206421</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1504,7 +1504,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7082325220108032</v>
+        <v>0.6990674138069153</v>
       </c>
       <c r="J25" t="n">
         <v>2</v>
@@ -1513,7 +1513,7 @@
         <v>10.75</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2469782829284668</v>
+        <v>0.2393222749233246</v>
       </c>
       <c r="M25" t="n">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>0.6910133957862854</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8412248492240906</v>
+        <v>0.8816059231758118</v>
       </c>
       <c r="D26" t="n">
         <v>3</v>
@@ -1539,7 +1539,7 @@
         <v>17.125</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7480762600898743</v>
+        <v>0.7814335823059082</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
@@ -1548,7 +1548,7 @@
         <v>3.138888888888889</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6513378024101257</v>
+        <v>0.6432872414588928</v>
       </c>
       <c r="J26" t="n">
         <v>3</v>
@@ -1557,7 +1557,7 @@
         <v>19.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4035640358924866</v>
+        <v>0.4144824743270874</v>
       </c>
       <c r="M26" t="n">
         <v>5</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0.8658062815666199</v>
+        <v>0.8769439458847046</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
@@ -1581,7 +1581,7 @@
         <v>11.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7866309881210327</v>
+        <v>0.828627347946167</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
@@ -1590,7 +1590,7 @@
         <v>11.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5678707361221313</v>
+        <v>0.5368509888648987</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -1599,7 +1599,7 @@
         <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4784495830535889</v>
+        <v>0.527858555316925</v>
       </c>
       <c r="M27" t="n">
         <v>5</v>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.6154610514640808</v>
+        <v>0.607061505317688</v>
       </c>
       <c r="D28" t="n">
         <v>3</v>
@@ -1623,7 +1623,7 @@
         <v>18.625</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8362463712692261</v>
+        <v>0.8441482782363892</v>
       </c>
       <c r="G28" t="n">
         <v>3</v>
@@ -1632,7 +1632,7 @@
         <v>14.66666666666667</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5934990644454956</v>
+        <v>0.5821720361709595</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -1641,7 +1641,7 @@
         <v>14.25</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3260641396045685</v>
+        <v>0.3426088690757751</v>
       </c>
       <c r="M28" t="n">
         <v>5</v>
@@ -1658,7 +1658,7 @@
         <v>0.7346736788749695</v>
       </c>
       <c r="C29" t="n">
-        <v>0.814123809337616</v>
+        <v>0.793099045753479</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
@@ -1667,7 +1667,7 @@
         <v>7.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8158693313598633</v>
+        <v>0.8312101364135742</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
@@ -1676,7 +1676,7 @@
         <v>4.805555555555555</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6506258845329285</v>
+        <v>0.7213341593742371</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -1685,7 +1685,7 @@
         <v>12</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4461143910884857</v>
+        <v>0.4705242514610291</v>
       </c>
       <c r="M29" t="n">
         <v>5</v>
@@ -1702,7 +1702,7 @@
         <v>0.8053781986236572</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3758595287799835</v>
+        <v>0.3813902735710144</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
@@ -1711,7 +1711,7 @@
         <v>12.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6646680235862732</v>
+        <v>0.6811315417289734</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1720,7 +1720,7 @@
         <v>5.222222222222222</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5413435697555542</v>
+        <v>0.5299422144889832</v>
       </c>
       <c r="J30" t="n">
         <v>2</v>
@@ -1729,7 +1729,7 @@
         <v>12</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5761783123016357</v>
+        <v>0.5594164133071899</v>
       </c>
       <c r="M30" t="n">
         <v>5</v>
@@ -1746,7 +1746,7 @@
         <v>0.5553000569343567</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5196549892425537</v>
+        <v>0.5204893350601196</v>
       </c>
       <c r="D31" t="n">
         <v>2</v>
@@ -1755,7 +1755,7 @@
         <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8625658750534058</v>
+        <v>0.8679301738739014</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
@@ -1764,7 +1764,7 @@
         <v>5.472222222222222</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4720396995544434</v>
+        <v>0.5456461906433105</v>
       </c>
       <c r="J31" t="n">
         <v>2</v>
@@ -1773,7 +1773,7 @@
         <v>10</v>
       </c>
       <c r="L31" t="n">
-        <v>0.4710604250431061</v>
+        <v>0.4540304839611053</v>
       </c>
       <c r="M31" t="n">
         <v>5</v>
@@ -1790,7 +1790,7 @@
         <v>0.7601224184036255</v>
       </c>
       <c r="C32" t="n">
-        <v>0.585332989692688</v>
+        <v>0.5783311128616333</v>
       </c>
       <c r="D32" t="n">
         <v>2</v>
@@ -1799,7 +1799,7 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9636943340301514</v>
+        <v>0.9508928656578064</v>
       </c>
       <c r="G32" t="n">
         <v>1</v>
@@ -1808,7 +1808,7 @@
         <v>3.944444444444445</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7046035528182983</v>
+        <v>0.6934462189674377</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -1817,7 +1817,7 @@
         <v>15.5</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5699288845062256</v>
+        <v>0.5025344491004944</v>
       </c>
       <c r="M32" t="n">
         <v>5</v>
@@ -1834,7 +1834,7 @@
         <v>0.725404679775238</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8791057467460632</v>
+        <v>0.8892443776130676</v>
       </c>
       <c r="D33" t="n">
         <v>2</v>
@@ -1843,7 +1843,7 @@
         <v>7</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7121675610542297</v>
+        <v>0.6633697152137756</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>2.333333333333333</v>
       </c>
       <c r="I33" t="n">
-        <v>0.593518078327179</v>
+        <v>0.6065324544906616</v>
       </c>
       <c r="J33" t="n">
         <v>2</v>
@@ -1861,7 +1861,7 @@
         <v>13.75</v>
       </c>
       <c r="L33" t="n">
-        <v>0.5197461843490601</v>
+        <v>0.4970918595790863</v>
       </c>
       <c r="M33" t="n">
         <v>5</v>
@@ -1878,7 +1878,7 @@
         <v>0.7136371731758118</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8632532358169556</v>
+        <v>0.8538606762886047</v>
       </c>
       <c r="D34" t="n">
         <v>2</v>
@@ -1887,7 +1887,7 @@
         <v>6.75</v>
       </c>
       <c r="F34" t="n">
-        <v>0.929176926612854</v>
+        <v>0.9543975591659546</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -1896,7 +1896,7 @@
         <v>9.138888888888889</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8822783827781677</v>
+        <v>0.8708898425102234</v>
       </c>
       <c r="J34" t="n">
         <v>2</v>
@@ -1905,7 +1905,7 @@
         <v>13</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4101955592632294</v>
+        <v>0.3971882462501526</v>
       </c>
       <c r="M34" t="n">
         <v>5</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.9046720266342163</v>
+        <v>0.8834399580955505</v>
       </c>
       <c r="D35" t="n">
         <v>2</v>
@@ -1929,7 +1929,7 @@
         <v>6.125</v>
       </c>
       <c r="F35" t="n">
-        <v>0.808963418006897</v>
+        <v>0.813863217830658</v>
       </c>
       <c r="G35" t="n">
         <v>2</v>
@@ -1938,7 +1938,7 @@
         <v>5.361111111111111</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7217451333999634</v>
+        <v>0.7348346710205078</v>
       </c>
       <c r="J35" t="n">
         <v>2</v>
@@ -1947,7 +1947,7 @@
         <v>13.25</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4133288860321045</v>
+        <v>0.4020260274410248</v>
       </c>
       <c r="M35" t="n">
         <v>5</v>
@@ -1964,7 +1964,7 @@
         <v>0.6483189463615417</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5326045751571655</v>
+        <v>0.568334698677063</v>
       </c>
       <c r="D36" t="n">
         <v>2</v>
@@ -1973,7 +1973,7 @@
         <v>13.875</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8536567687988281</v>
+        <v>0.8528813123703003</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
@@ -1982,7 +1982,7 @@
         <v>3.277777777777778</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6801987290382385</v>
+        <v>0.6723500490188599</v>
       </c>
       <c r="J36" t="n">
         <v>2</v>
@@ -1991,7 +1991,7 @@
         <v>13.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5570284724235535</v>
+        <v>0.4860395193099976</v>
       </c>
       <c r="M36" t="n">
         <v>5</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0.7443169355392456</v>
+        <v>0.7305679321289062</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -2015,7 +2015,7 @@
         <v>3.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.642186164855957</v>
+        <v>0.7175344824790955</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
@@ -2024,7 +2024,7 @@
         <v>2.722222222222222</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4312816262245178</v>
+        <v>0.5144662261009216</v>
       </c>
       <c r="J37" t="n">
         <v>2</v>
@@ -2033,7 +2033,7 @@
         <v>13</v>
       </c>
       <c r="L37" t="n">
-        <v>0.475962370634079</v>
+        <v>0.3859632611274719</v>
       </c>
       <c r="M37" t="n">
         <v>5</v>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0.8192140460014343</v>
+        <v>0.8158943653106689</v>
       </c>
       <c r="D38" t="n">
         <v>2</v>
@@ -2057,7 +2057,7 @@
         <v>9.125</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9089840650558472</v>
+        <v>0.9371998310089111</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
@@ -2066,7 +2066,7 @@
         <v>5.611111111111111</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7479307055473328</v>
+        <v>0.7390919923782349</v>
       </c>
       <c r="J38" t="n">
         <v>2</v>
@@ -2075,7 +2075,7 @@
         <v>8</v>
       </c>
       <c r="L38" t="n">
-        <v>0.3944857120513916</v>
+        <v>0.3591636121273041</v>
       </c>
       <c r="M38" t="n">
         <v>5</v>
@@ -2092,7 +2092,7 @@
         <v>0.6702994704246521</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6466858983039856</v>
+        <v>0.7027022838592529</v>
       </c>
       <c r="D39" t="n">
         <v>3</v>
@@ -2101,7 +2101,7 @@
         <v>14.375</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7887897491455078</v>
+        <v>0.7442232370376587</v>
       </c>
       <c r="G39" t="n">
         <v>2</v>
@@ -2110,7 +2110,7 @@
         <v>4.611111111111111</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5108057856559753</v>
+        <v>0.4414577782154083</v>
       </c>
       <c r="J39" t="n">
         <v>2</v>
@@ -2119,7 +2119,7 @@
         <v>14</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4298136532306671</v>
+        <v>0.4340223371982574</v>
       </c>
       <c r="M39" t="n">
         <v>5</v>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.5765455961227417</v>
+        <v>0.562260627746582</v>
       </c>
       <c r="D40" t="n">
         <v>2</v>
@@ -2143,7 +2143,7 @@
         <v>8.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5545858144760132</v>
+        <v>0.5850237607955933</v>
       </c>
       <c r="G40" t="n">
         <v>1</v>
@@ -2152,7 +2152,7 @@
         <v>2.777777777777778</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4654823541641235</v>
+        <v>0.4734649062156677</v>
       </c>
       <c r="J40" t="n">
         <v>2</v>
@@ -2161,7 +2161,7 @@
         <v>8</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1780493259429932</v>
+        <v>0.1754348278045654</v>
       </c>
       <c r="M40" t="n">
         <v>5</v>
@@ -2178,7 +2178,7 @@
         <v>0.7499797344207764</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6558920741081238</v>
+        <v>0.6957670450210571</v>
       </c>
       <c r="D41" t="n">
         <v>2</v>
@@ -2187,7 +2187,7 @@
         <v>9.375</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8691114187240601</v>
+        <v>0.8828771114349365</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
@@ -2196,7 +2196,7 @@
         <v>5.805555555555555</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5499748587608337</v>
+        <v>0.604182243347168</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -2205,7 +2205,7 @@
         <v>19.5</v>
       </c>
       <c r="L41" t="n">
-        <v>0.7408808469772339</v>
+        <v>0.6585932970046997</v>
       </c>
       <c r="M41" t="n">
         <v>5</v>
@@ -2222,7 +2222,7 @@
         <v>0.7396210432052612</v>
       </c>
       <c r="C42" t="n">
-        <v>0.4671673774719238</v>
+        <v>0.4907616376876831</v>
       </c>
       <c r="D42" t="n">
         <v>2</v>
@@ -2231,7 +2231,7 @@
         <v>12.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0.6240038871765137</v>
+        <v>0.6348346471786499</v>
       </c>
       <c r="G42" t="n">
         <v>2</v>
@@ -2240,7 +2240,7 @@
         <v>5.305555555555555</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6677995920181274</v>
+        <v>0.592828631401062</v>
       </c>
       <c r="J42" t="n">
         <v>3</v>
@@ -2249,7 +2249,7 @@
         <v>22.75</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7445811629295349</v>
+        <v>0.7408697605133057</v>
       </c>
       <c r="M42" t="n">
         <v>5</v>
@@ -2266,7 +2266,7 @@
         <v>0.6149531006813049</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7265245914459229</v>
+        <v>0.7344480156898499</v>
       </c>
       <c r="D43" t="n">
         <v>2</v>
@@ -2275,7 +2275,7 @@
         <v>6.625</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8349423408508301</v>
+        <v>0.8574726581573486</v>
       </c>
       <c r="G43" t="n">
         <v>2</v>
@@ -2284,7 +2284,7 @@
         <v>6.527777777777778</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6727114915847778</v>
+        <v>0.6608766317367554</v>
       </c>
       <c r="J43" t="n">
         <v>2</v>
@@ -2293,7 +2293,7 @@
         <v>12.75</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8228269219398499</v>
+        <v>0.8153918981552124</v>
       </c>
       <c r="M43" t="n">
         <v>5</v>
@@ -2310,7 +2310,7 @@
         <v>0.718414843082428</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5942167043685913</v>
+        <v>0.5766165256500244</v>
       </c>
       <c r="D44" t="n">
         <v>2</v>
@@ -2319,7 +2319,7 @@
         <v>6.5</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7714336514472961</v>
+        <v>0.7705869674682617</v>
       </c>
       <c r="G44" t="n">
         <v>2</v>
@@ -2328,7 +2328,7 @@
         <v>11.52777777777778</v>
       </c>
       <c r="I44" t="n">
-        <v>0.55228191614151</v>
+        <v>0.596579909324646</v>
       </c>
       <c r="J44" t="n">
         <v>3</v>
@@ -2337,7 +2337,7 @@
         <v>17</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7768943905830383</v>
+        <v>0.7567116022109985</v>
       </c>
       <c r="M44" t="n">
         <v>5</v>
@@ -2354,7 +2354,7 @@
         <v>0.6837395429611206</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6561801433563232</v>
+        <v>0.6096981167793274</v>
       </c>
       <c r="D45" t="n">
         <v>2</v>
@@ -2370,7 +2370,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="I45" t="n">
-        <v>0.771435022354126</v>
+        <v>0.7711293697357178</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
@@ -2379,7 +2379,7 @@
         <v>12.75</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7862091064453125</v>
+        <v>0.8129456639289856</v>
       </c>
       <c r="M45" t="n">
         <v>5</v>
@@ -2403,7 +2403,7 @@
         <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8403061628341675</v>
+        <v>0.8187689781188965</v>
       </c>
       <c r="G46" t="n">
         <v>2</v>
@@ -2412,7 +2412,7 @@
         <v>5.472222222222222</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7586362361907959</v>
+        <v>0.7473474740982056</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
@@ -2421,7 +2421,7 @@
         <v>12.75</v>
       </c>
       <c r="L46" t="n">
-        <v>0.8256916999816895</v>
+        <v>0.8208481073379517</v>
       </c>
       <c r="M46" t="n">
         <v>5</v>
@@ -2438,7 +2438,7 @@
         <v>0.7549548149108887</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7662181854248047</v>
+        <v>0.7713137865066528</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
@@ -2447,7 +2447,7 @@
         <v>3.625</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8007938861846924</v>
+        <v>0.8239177465438843</v>
       </c>
       <c r="G47" t="n">
         <v>2</v>
@@ -2456,7 +2456,7 @@
         <v>4.944444444444445</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6235235929489136</v>
+        <v>0.6642919778823853</v>
       </c>
       <c r="J47" t="n">
         <v>3</v>
@@ -2465,7 +2465,7 @@
         <v>21.75</v>
       </c>
       <c r="L47" t="n">
-        <v>0.8322996497154236</v>
+        <v>0.8355075716972351</v>
       </c>
       <c r="M47" t="n">
         <v>5</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.5767502188682556</v>
+        <v>0.4807614684104919</v>
       </c>
       <c r="D48" t="n">
         <v>2</v>
@@ -2489,7 +2489,7 @@
         <v>10.5</v>
       </c>
       <c r="F48" t="n">
-        <v>0.79413902759552</v>
+        <v>0.7722196578979492</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
@@ -2498,7 +2498,7 @@
         <v>4.833333333333333</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6804496049880981</v>
+        <v>0.75631183385849</v>
       </c>
       <c r="J48" t="n">
         <v>3</v>
@@ -2507,7 +2507,7 @@
         <v>17</v>
       </c>
       <c r="L48" t="n">
-        <v>0.8071174621582031</v>
+        <v>0.7652710676193237</v>
       </c>
       <c r="M48" t="n">
         <v>5</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.630707859992981</v>
+        <v>0.6301015019416809</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
@@ -2531,7 +2531,7 @@
         <v>4.375</v>
       </c>
       <c r="F49" t="n">
-        <v>0.69856196641922</v>
+        <v>0.6871287822723389</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -2540,7 +2540,7 @@
         <v>2.25</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6555577516555786</v>
+        <v>0.6925300359725952</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -2549,7 +2549,7 @@
         <v>14.5</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7552855610847473</v>
+        <v>0.7562372088432312</v>
       </c>
       <c r="M49" t="n">
         <v>5</v>
@@ -2566,7 +2566,7 @@
         <v>0.7674471735954285</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6798661947250366</v>
+        <v>0.7203370928764343</v>
       </c>
       <c r="D50" t="n">
         <v>3</v>
@@ -2575,7 +2575,7 @@
         <v>39.625</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8281192779541016</v>
+        <v>0.8251938223838806</v>
       </c>
       <c r="G50" t="n">
         <v>2</v>
@@ -2584,7 +2584,7 @@
         <v>12.97222222222222</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6183634996414185</v>
+        <v>0.5861741304397583</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -2593,7 +2593,7 @@
         <v>17</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8376776576042175</v>
+        <v>0.8191654086112976</v>
       </c>
       <c r="M50" t="n">
         <v>5</v>
@@ -2617,7 +2617,7 @@
         <v>2.375</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8076744675636292</v>
+        <v>0.7790354490280151</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -2626,7 +2626,7 @@
         <v>4.75</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7160515785217285</v>
+        <v>0.7151005268096924</v>
       </c>
       <c r="J51" t="n">
         <v>3</v>
@@ -2646,7 +2646,7 @@
         <v>0.6722381114959717</v>
       </c>
       <c r="C52" t="n">
-        <v>0.5897393226623535</v>
+        <v>0.4252687096595764</v>
       </c>
       <c r="D52" t="n">
         <v>2</v>
@@ -2655,7 +2655,7 @@
         <v>6.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7401095628738403</v>
+        <v>0.7673631906509399</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -2664,7 +2664,7 @@
         <v>8.416666666666666</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7324116826057434</v>
+        <v>0.7057728171348572</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
@@ -2673,7 +2673,7 @@
         <v>12.5</v>
       </c>
       <c r="L52" t="n">
-        <v>0.853125274181366</v>
+        <v>0.8242127299308777</v>
       </c>
       <c r="M52" t="n">
         <v>5</v>
@@ -2690,7 +2690,7 @@
         <v>0.6771166920661926</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8164691925048828</v>
+        <v>0.734459400177002</v>
       </c>
       <c r="D53" t="n">
         <v>3</v>
@@ -2699,7 +2699,7 @@
         <v>16.625</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7367845773696899</v>
+        <v>0.7422847747802734</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
@@ -2708,7 +2708,7 @@
         <v>8.638888888888889</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4431985020637512</v>
+        <v>0.4048557877540588</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -2717,7 +2717,7 @@
         <v>16.75</v>
       </c>
       <c r="L53" t="n">
-        <v>0.8409246802330017</v>
+        <v>0.8284233808517456</v>
       </c>
       <c r="M53" t="n">
         <v>5</v>
@@ -2734,7 +2734,7 @@
         <v>0.668490469455719</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8106653690338135</v>
+        <v>0.6092110872268677</v>
       </c>
       <c r="D54" t="n">
         <v>2</v>
@@ -2743,7 +2743,7 @@
         <v>9.125</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8692485094070435</v>
+        <v>0.8865286707878113</v>
       </c>
       <c r="G54" t="n">
         <v>2</v>
@@ -2752,7 +2752,7 @@
         <v>4.472222222222222</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6059101819992065</v>
+        <v>0.5812996625900269</v>
       </c>
       <c r="J54" t="n">
         <v>2</v>
@@ -2761,7 +2761,7 @@
         <v>14</v>
       </c>
       <c r="L54" t="n">
-        <v>0.8097207546234131</v>
+        <v>0.7903897762298584</v>
       </c>
       <c r="M54" t="n">
         <v>5</v>
@@ -2778,7 +2778,7 @@
         <v>0.7178375124931335</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6438583135604858</v>
+        <v>0.6694441437721252</v>
       </c>
       <c r="D55" t="n">
         <v>2</v>
@@ -2787,7 +2787,7 @@
         <v>9.625</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8849895596504211</v>
+        <v>0.8956944942474365</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -2796,7 +2796,7 @@
         <v>10.63888888888889</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7001253962516785</v>
+        <v>0.7092143893241882</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
@@ -2805,7 +2805,7 @@
         <v>23.25</v>
       </c>
       <c r="L55" t="n">
-        <v>0.7801516056060791</v>
+        <v>0.7458691000938416</v>
       </c>
       <c r="M55" t="n">
         <v>5</v>
@@ -2822,7 +2822,7 @@
         <v>0.6353439092636108</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8036994934082031</v>
+        <v>0.775083065032959</v>
       </c>
       <c r="D56" t="n">
         <v>2</v>
@@ -2831,7 +2831,7 @@
         <v>7.625</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5716754198074341</v>
+        <v>0.5484966039657593</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>2.027777777777778</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8083363771438599</v>
+        <v>0.7702000141143799</v>
       </c>
       <c r="J56" t="n">
         <v>2</v>
@@ -2849,7 +2849,7 @@
         <v>14</v>
       </c>
       <c r="L56" t="n">
-        <v>0.7946088314056396</v>
+        <v>0.784770131111145</v>
       </c>
       <c r="M56" t="n">
         <v>5</v>
@@ -2866,7 +2866,7 @@
         <v>0.6450530886650085</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7809160947799683</v>
+        <v>0.7242860794067383</v>
       </c>
       <c r="D57" t="n">
         <v>2</v>
@@ -2875,7 +2875,7 @@
         <v>12.625</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8595689535140991</v>
+        <v>0.8708518743515015</v>
       </c>
       <c r="G57" t="n">
         <v>2</v>
@@ -2884,7 +2884,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="I57" t="n">
-        <v>0.6548870801925659</v>
+        <v>0.6814480423927307</v>
       </c>
       <c r="J57" t="n">
         <v>3</v>
@@ -2893,7 +2893,7 @@
         <v>15.75</v>
       </c>
       <c r="L57" t="n">
-        <v>0.7873062491416931</v>
+        <v>0.7798944711685181</v>
       </c>
       <c r="M57" t="n">
         <v>5</v>
@@ -2910,7 +2910,7 @@
         <v>0.6993920803070068</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6140484809875488</v>
+        <v>0.6567279696464539</v>
       </c>
       <c r="D58" t="n">
         <v>2</v>
@@ -2919,7 +2919,7 @@
         <v>7.125</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6744243502616882</v>
+        <v>0.6848664283752441</v>
       </c>
       <c r="G58" t="n">
         <v>2</v>
@@ -2928,7 +2928,7 @@
         <v>5.861111111111111</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6811982393264771</v>
+        <v>0.6492124795913696</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
@@ -2937,7 +2937,7 @@
         <v>10.25</v>
       </c>
       <c r="L58" t="n">
-        <v>0.8528329133987427</v>
+        <v>0.8582455515861511</v>
       </c>
       <c r="M58" t="n">
         <v>5</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0.8101041316986084</v>
+        <v>0.858817458152771</v>
       </c>
       <c r="D59" t="n">
         <v>3</v>
@@ -2961,7 +2961,7 @@
         <v>16.5</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7522904872894287</v>
+        <v>0.7681507468223572</v>
       </c>
       <c r="G59" t="n">
         <v>2</v>
@@ -2970,7 +2970,7 @@
         <v>8.194444444444445</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7278639078140259</v>
+        <v>0.6775465607643127</v>
       </c>
       <c r="J59" t="n">
         <v>3</v>
@@ -2979,7 +2979,7 @@
         <v>16.25</v>
       </c>
       <c r="L59" t="n">
-        <v>0.8447270393371582</v>
+        <v>0.8463480472564697</v>
       </c>
       <c r="M59" t="n">
         <v>5</v>
@@ -2996,7 +2996,7 @@
         <v>0.7250692248344421</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7523071765899658</v>
+        <v>0.7537139654159546</v>
       </c>
       <c r="D60" t="n">
         <v>2</v>
@@ -3005,7 +3005,7 @@
         <v>6.5</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8975330591201782</v>
+        <v>0.8878639936447144</v>
       </c>
       <c r="G60" t="n">
         <v>2</v>
@@ -3014,7 +3014,7 @@
         <v>5.527777777777778</v>
       </c>
       <c r="I60" t="n">
-        <v>0.7482423782348633</v>
+        <v>0.7297344207763672</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -3023,7 +3023,7 @@
         <v>15.75</v>
       </c>
       <c r="L60" t="n">
-        <v>0.7571569681167603</v>
+        <v>0.8062491416931152</v>
       </c>
       <c r="M60" t="n">
         <v>5</v>
@@ -3040,7 +3040,7 @@
         <v>0.6863186359405518</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6237326264381409</v>
+        <v>0.6205778121948242</v>
       </c>
       <c r="D61" t="n">
         <v>2</v>
@@ -3049,7 +3049,7 @@
         <v>4.625</v>
       </c>
       <c r="F61" t="n">
-        <v>0.849042534828186</v>
+        <v>0.8390263319015503</v>
       </c>
       <c r="G61" t="n">
         <v>2</v>
@@ -3058,7 +3058,7 @@
         <v>7.25</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6740673780441284</v>
+        <v>0.6632840633392334</v>
       </c>
       <c r="J61" t="n">
         <v>2</v>
@@ -3067,7 +3067,7 @@
         <v>13</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8107616901397705</v>
+        <v>0.8324596881866455</v>
       </c>
       <c r="M61" t="n">
         <v>5</v>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.7249420881271362</v>
+        <v>0.7412936091423035</v>
       </c>
       <c r="D62" t="n">
         <v>2</v>
@@ -3091,7 +3091,7 @@
         <v>9.5</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9558784365653992</v>
+        <v>0.9666719436645508</v>
       </c>
       <c r="G62" t="n">
         <v>2</v>
@@ -3114,7 +3114,7 @@
         <v>0.612175464630127</v>
       </c>
       <c r="C63" t="n">
-        <v>0.3990725576877594</v>
+        <v>0.3519615530967712</v>
       </c>
       <c r="D63" t="n">
         <v>2</v>
@@ -3123,7 +3123,7 @@
         <v>4.75</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7637692093849182</v>
+        <v>0.7365808486938477</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -3132,7 +3132,7 @@
         <v>8.333333333333334</v>
       </c>
       <c r="I63" t="n">
-        <v>0.64626544713974</v>
+        <v>0.6532529592514038</v>
       </c>
       <c r="J63" t="n">
         <v>2</v>
@@ -3141,7 +3141,7 @@
         <v>11.5</v>
       </c>
       <c r="L63" t="n">
-        <v>0.7233735322952271</v>
+        <v>0.7725542187690735</v>
       </c>
       <c r="M63" t="n">
         <v>5</v>
@@ -3158,7 +3158,7 @@
         <v>0.6431297063827515</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6224327683448792</v>
+        <v>0.6601948738098145</v>
       </c>
       <c r="D64" t="n">
         <v>2</v>
@@ -3167,7 +3167,7 @@
         <v>8.125</v>
       </c>
       <c r="F64" t="n">
-        <v>0.7626586556434631</v>
+        <v>0.7785974144935608</v>
       </c>
       <c r="G64" t="n">
         <v>2</v>
@@ -3176,7 +3176,7 @@
         <v>5.666666666666667</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5313394665718079</v>
+        <v>0.5290473103523254</v>
       </c>
       <c r="J64" t="n">
         <v>3</v>
@@ -3185,7 +3185,7 @@
         <v>14.5</v>
       </c>
       <c r="L64" t="n">
-        <v>0.7505477666854858</v>
+        <v>0.7257453203201294</v>
       </c>
       <c r="M64" t="n">
         <v>5</v>
@@ -3202,7 +3202,7 @@
         <v>0.6946020126342773</v>
       </c>
       <c r="C65" t="n">
-        <v>0.71296226978302</v>
+        <v>0.6828508377075195</v>
       </c>
       <c r="D65" t="n">
         <v>2</v>
@@ -3211,7 +3211,7 @@
         <v>8.625</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8677858114242554</v>
+        <v>0.8506739735603333</v>
       </c>
       <c r="G65" t="n">
         <v>2</v>
@@ -3220,7 +3220,7 @@
         <v>11.77777777777778</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3945671319961548</v>
+        <v>0.3770625591278076</v>
       </c>
       <c r="J65" t="n">
         <v>3</v>
@@ -3229,7 +3229,7 @@
         <v>18.25</v>
       </c>
       <c r="L65" t="n">
-        <v>0.4230709373950958</v>
+        <v>0.4056327044963837</v>
       </c>
       <c r="M65" t="n">
         <v>5</v>
@@ -3246,7 +3246,7 @@
         <v>0.7090784907341003</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6411948204040527</v>
+        <v>0.6414574384689331</v>
       </c>
       <c r="D66" t="n">
         <v>2</v>
@@ -3255,7 +3255,7 @@
         <v>10.375</v>
       </c>
       <c r="F66" t="n">
-        <v>0.8333410024642944</v>
+        <v>0.8100980520248413</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -3264,7 +3264,7 @@
         <v>8.027777777777779</v>
       </c>
       <c r="I66" t="n">
-        <v>0.7328341603279114</v>
+        <v>0.781579852104187</v>
       </c>
       <c r="J66" t="n">
         <v>3</v>
@@ -3273,7 +3273,7 @@
         <v>30.75</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5204522013664246</v>
+        <v>0.5035629272460938</v>
       </c>
       <c r="M66" t="n">
         <v>5</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0.4353178739547729</v>
+        <v>0.4383200407028198</v>
       </c>
       <c r="D67" t="n">
         <v>2</v>
@@ -3297,7 +3297,7 @@
         <v>7.25</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8049399852752686</v>
+        <v>0.7892045974731445</v>
       </c>
       <c r="G67" t="n">
         <v>2</v>
@@ -3306,7 +3306,7 @@
         <v>6</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7847964763641357</v>
+        <v>0.4944402575492859</v>
       </c>
       <c r="J67" t="n">
         <v>2</v>
@@ -3315,7 +3315,7 @@
         <v>9.75</v>
       </c>
       <c r="L67" t="n">
-        <v>0.7485059499740601</v>
+        <v>0.7541478872299194</v>
       </c>
       <c r="M67" t="n">
         <v>5</v>
@@ -3332,7 +3332,7 @@
         <v>0.6992693543434143</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5985871553421021</v>
+        <v>0.6180155277252197</v>
       </c>
       <c r="D68" t="n">
         <v>2</v>
@@ -3341,7 +3341,7 @@
         <v>10.625</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4462863504886627</v>
+        <v>0.3427488803863525</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -3350,7 +3350,7 @@
         <v>1.694444444444444</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6014138460159302</v>
+        <v>0.6152088046073914</v>
       </c>
       <c r="J68" t="n">
         <v>2</v>
@@ -3359,7 +3359,7 @@
         <v>10.75</v>
       </c>
       <c r="L68" t="n">
-        <v>0.7206407189369202</v>
+        <v>0.7033752202987671</v>
       </c>
       <c r="M68" t="n">
         <v>5</v>
@@ -3376,7 +3376,7 @@
         <v>0.6104212999343872</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8108614683151245</v>
+        <v>0.7450288534164429</v>
       </c>
       <c r="D69" t="n">
         <v>3</v>
@@ -3385,7 +3385,7 @@
         <v>15.75</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8469384908676147</v>
+        <v>0.7991011142730713</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -3394,7 +3394,7 @@
         <v>5.5</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6469140648841858</v>
+        <v>0.7318075895309448</v>
       </c>
       <c r="J69" t="n">
         <v>3</v>
@@ -3403,7 +3403,7 @@
         <v>15.75</v>
       </c>
       <c r="L69" t="n">
-        <v>0.7646991014480591</v>
+        <v>0.7273932099342346</v>
       </c>
       <c r="M69" t="n">
         <v>5</v>
@@ -3420,7 +3420,7 @@
         <v>0.5988723635673523</v>
       </c>
       <c r="C70" t="n">
-        <v>0.5363293886184692</v>
+        <v>0.5195608139038086</v>
       </c>
       <c r="D70" t="n">
         <v>2</v>
@@ -3429,7 +3429,7 @@
         <v>5</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8536738157272339</v>
+        <v>0.8425300717353821</v>
       </c>
       <c r="G70" t="n">
         <v>1</v>
@@ -3438,7 +3438,7 @@
         <v>2.972222222222222</v>
       </c>
       <c r="I70" t="n">
-        <v>0.6328356266021729</v>
+        <v>0.6699033975601196</v>
       </c>
       <c r="J70" t="n">
         <v>3</v>
@@ -3447,7 +3447,7 @@
         <v>15.25</v>
       </c>
       <c r="L70" t="n">
-        <v>0.7372584342956543</v>
+        <v>0.7330653071403503</v>
       </c>
       <c r="M70" t="n">
         <v>5</v>
@@ -3464,7 +3464,7 @@
         <v>0.6498538851737976</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2370181977748871</v>
+        <v>0.1953805983066559</v>
       </c>
       <c r="D71" t="n">
         <v>2</v>
@@ -3473,7 +3473,7 @@
         <v>5.625</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7914314270019531</v>
+        <v>0.8431268930435181</v>
       </c>
       <c r="G71" t="n">
         <v>2</v>
@@ -3482,7 +3482,7 @@
         <v>7.055555555555555</v>
       </c>
       <c r="I71" t="n">
-        <v>0.7586043477058411</v>
+        <v>0.7685186266899109</v>
       </c>
       <c r="J71" t="n">
         <v>3</v>
@@ -3491,7 +3491,7 @@
         <v>15.75</v>
       </c>
       <c r="L71" t="n">
-        <v>0.8059864640235901</v>
+        <v>0.797598123550415</v>
       </c>
       <c r="M71" t="n">
         <v>5</v>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0.7949709296226501</v>
+        <v>0.7631727457046509</v>
       </c>
       <c r="D72" t="n">
         <v>2</v>
@@ -3515,7 +3515,7 @@
         <v>8.75</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3813205361366272</v>
+        <v>0.3751220405101776</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -3524,7 +3524,7 @@
         <v>2.666666666666667</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5995960235595703</v>
+        <v>0.5634266138076782</v>
       </c>
       <c r="J72" t="n">
         <v>3</v>
@@ -3533,7 +3533,7 @@
         <v>27.25</v>
       </c>
       <c r="L72" t="n">
-        <v>0.7521629929542542</v>
+        <v>0.7280569672584534</v>
       </c>
       <c r="M72" t="n">
         <v>5</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0.8847963213920593</v>
+        <v>0.8782058358192444</v>
       </c>
       <c r="D73" t="n">
         <v>2</v>
@@ -3557,7 +3557,7 @@
         <v>10.125</v>
       </c>
       <c r="F73" t="n">
-        <v>0.8375255465507507</v>
+        <v>0.8630804419517517</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
@@ -3566,7 +3566,7 @@
         <v>5.138888888888889</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7207282185554504</v>
+        <v>0.7217512130737305</v>
       </c>
       <c r="J73" t="n">
         <v>3</v>
@@ -3575,7 +3575,7 @@
         <v>19.5</v>
       </c>
       <c r="L73" t="n">
-        <v>0.817619800567627</v>
+        <v>0.8066605925559998</v>
       </c>
       <c r="M73" t="n">
         <v>5</v>
@@ -3592,7 +3592,7 @@
         <v>0.6694533824920654</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6097773313522339</v>
+        <v>0.5820635557174683</v>
       </c>
       <c r="D74" t="n">
         <v>2</v>
@@ -3601,7 +3601,7 @@
         <v>6.375</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5148425102233887</v>
+        <v>0.518162727355957</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
@@ -3610,7 +3610,7 @@
         <v>2.666666666666667</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8540136814117432</v>
+        <v>0.8689728975296021</v>
       </c>
       <c r="J74" t="n">
         <v>3</v>
@@ -3619,7 +3619,7 @@
         <v>18.25</v>
       </c>
       <c r="L74" t="n">
-        <v>0.8077247738838196</v>
+        <v>0.8073030114173889</v>
       </c>
       <c r="M74" t="n">
         <v>5</v>
@@ -3636,7 +3636,7 @@
         <v>0.6466736793518066</v>
       </c>
       <c r="C75" t="n">
-        <v>0.5130618810653687</v>
+        <v>0.4863564372062683</v>
       </c>
       <c r="D75" t="n">
         <v>2</v>
@@ -3645,7 +3645,7 @@
         <v>7</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8219517469406128</v>
+        <v>0.8264564275741577</v>
       </c>
       <c r="G75" t="n">
         <v>2</v>
@@ -3654,7 +3654,7 @@
         <v>4.027777777777778</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8248050212860107</v>
+        <v>0.828116774559021</v>
       </c>
       <c r="J75" t="n">
         <v>3</v>
@@ -3663,7 +3663,7 @@
         <v>14.5</v>
       </c>
       <c r="L75" t="n">
-        <v>0.8208680152893066</v>
+        <v>0.8039629459381104</v>
       </c>
       <c r="M75" t="n">
         <v>5</v>
@@ -3680,7 +3680,7 @@
         <v>0.7411791086196899</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8401663303375244</v>
+        <v>0.84639573097229</v>
       </c>
       <c r="D76" t="n">
         <v>2</v>
@@ -3689,7 +3689,7 @@
         <v>10.875</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7301994562149048</v>
+        <v>0.71324622631073</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
@@ -3698,7 +3698,7 @@
         <v>3.416666666666667</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7913839221000671</v>
+        <v>0.7905155420303345</v>
       </c>
       <c r="J76" t="n">
         <v>3</v>
@@ -3707,7 +3707,7 @@
         <v>22.75</v>
       </c>
       <c r="L76" t="n">
-        <v>0.7979096174240112</v>
+        <v>0.7445807456970215</v>
       </c>
       <c r="M76" t="n">
         <v>5</v>
@@ -3724,7 +3724,7 @@
         <v>0.6945134997367859</v>
       </c>
       <c r="C77" t="n">
-        <v>0.6302219033241272</v>
+        <v>0.5973350405693054</v>
       </c>
       <c r="D77" t="n">
         <v>2</v>
@@ -3733,7 +3733,7 @@
         <v>6.375</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5890752077102661</v>
+        <v>0.5523420572280884</v>
       </c>
       <c r="G77" t="n">
         <v>1</v>
@@ -3742,7 +3742,7 @@
         <v>3.222222222222222</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6004891395568848</v>
+        <v>0.6110572814941406</v>
       </c>
       <c r="J77" t="n">
         <v>3</v>
@@ -3751,7 +3751,7 @@
         <v>16</v>
       </c>
       <c r="L77" t="n">
-        <v>0.7639915943145752</v>
+        <v>0.7564640045166016</v>
       </c>
       <c r="M77" t="n">
         <v>5</v>
@@ -3768,7 +3768,7 @@
         <v>0.7413830757141113</v>
       </c>
       <c r="C78" t="n">
-        <v>0.8154322504997253</v>
+        <v>0.8422701358795166</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
@@ -3777,7 +3777,7 @@
         <v>2.75</v>
       </c>
       <c r="F78" t="n">
-        <v>0.8836448192596436</v>
+        <v>0.8829097151756287</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -3786,7 +3786,7 @@
         <v>7.527777777777778</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6988034248352051</v>
+        <v>0.7467659115791321</v>
       </c>
       <c r="J78" t="n">
         <v>3</v>
@@ -3795,7 +3795,7 @@
         <v>18.5</v>
       </c>
       <c r="L78" t="n">
-        <v>0.7868136167526245</v>
+        <v>0.8153367042541504</v>
       </c>
       <c r="M78" t="n">
         <v>5</v>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>0.7022662758827209</v>
+        <v>0.6560178995132446</v>
       </c>
       <c r="D79" t="n">
         <v>3</v>
@@ -3819,7 +3819,7 @@
         <v>14.375</v>
       </c>
       <c r="F79" t="n">
-        <v>0.663541316986084</v>
+        <v>0.7122644186019897</v>
       </c>
       <c r="G79" t="n">
         <v>2</v>
@@ -3828,7 +3828,7 @@
         <v>4.388888888888889</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5689557194709778</v>
+        <v>0.5590798854827881</v>
       </c>
       <c r="J79" t="n">
         <v>2</v>
@@ -3837,7 +3837,7 @@
         <v>12.5</v>
       </c>
       <c r="L79" t="n">
-        <v>0.7875045537948608</v>
+        <v>0.7619814872741699</v>
       </c>
       <c r="M79" t="n">
         <v>5</v>
@@ -3854,7 +3854,7 @@
         <v>0.6541247963905334</v>
       </c>
       <c r="C80" t="n">
-        <v>0.4602527022361755</v>
+        <v>0.4554100334644318</v>
       </c>
       <c r="D80" t="n">
         <v>2</v>
@@ -3863,7 +3863,7 @@
         <v>7</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8767517805099487</v>
+        <v>0.8565315008163452</v>
       </c>
       <c r="G80" t="n">
         <v>2</v>
@@ -3872,7 +3872,7 @@
         <v>6.416666666666667</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3804676532745361</v>
+        <v>0.3596215546131134</v>
       </c>
       <c r="J80" t="n">
         <v>3</v>
@@ -3881,7 +3881,7 @@
         <v>14.5</v>
       </c>
       <c r="L80" t="n">
-        <v>0.7800881862640381</v>
+        <v>0.7670828700065613</v>
       </c>
       <c r="M80" t="n">
         <v>5</v>
@@ -3903,7 +3903,7 @@
         <v>3.25</v>
       </c>
       <c r="F81" t="n">
-        <v>0.9307425022125244</v>
+        <v>0.947114109992981</v>
       </c>
       <c r="G81" t="n">
         <v>2</v>
@@ -3912,7 +3912,7 @@
         <v>4.861111111111111</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6316055655479431</v>
+        <v>0.7107834815979004</v>
       </c>
       <c r="J81" t="n">
         <v>3</v>
@@ -3921,7 +3921,7 @@
         <v>15.5</v>
       </c>
       <c r="L81" t="n">
-        <v>0.7768787145614624</v>
+        <v>0.746181845664978</v>
       </c>
       <c r="M81" t="n">
         <v>5</v>
@@ -3938,7 +3938,7 @@
         <v>0.7826205492019653</v>
       </c>
       <c r="C82" t="n">
-        <v>0.6559967994689941</v>
+        <v>0.6241066455841064</v>
       </c>
       <c r="D82" t="n">
         <v>2</v>
@@ -3947,7 +3947,7 @@
         <v>4.625</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9140844345092773</v>
+        <v>0.9273706674575806</v>
       </c>
       <c r="G82" t="n">
         <v>2</v>
@@ -3956,7 +3956,7 @@
         <v>4.833333333333333</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4367899596691132</v>
+        <v>0.5117122530937195</v>
       </c>
       <c r="J82" t="n">
         <v>3</v>
@@ -3965,7 +3965,7 @@
         <v>21.5</v>
       </c>
       <c r="L82" t="n">
-        <v>0.8079676628112793</v>
+        <v>0.7639646530151367</v>
       </c>
       <c r="M82" t="n">
         <v>5</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0.5796709060668945</v>
+        <v>0.6018962860107422</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
@@ -3989,7 +3989,7 @@
         <v>3.75</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6613198518753052</v>
+        <v>0.6160176396369934</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -3998,7 +3998,7 @@
         <v>3.805555555555555</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7510330677032471</v>
+        <v>0.7785196900367737</v>
       </c>
       <c r="J83" t="n">
         <v>3</v>
@@ -4007,7 +4007,7 @@
         <v>20.75</v>
       </c>
       <c r="L83" t="n">
-        <v>0.9093989133834839</v>
+        <v>0.914027214050293</v>
       </c>
       <c r="M83" t="n">
         <v>5</v>
@@ -4024,7 +4024,7 @@
         <v>0.7757197618484497</v>
       </c>
       <c r="C84" t="n">
-        <v>0.4806787371635437</v>
+        <v>0.4990387558937073</v>
       </c>
       <c r="D84" t="n">
         <v>2</v>
@@ -4033,7 +4033,7 @@
         <v>5.625</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8048185110092163</v>
+        <v>0.8152987957000732</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -4042,7 +4042,7 @@
         <v>3.611111111111111</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6873025894165039</v>
+        <v>0.7829991579055786</v>
       </c>
       <c r="J84" t="n">
         <v>3</v>
@@ -4051,7 +4051,7 @@
         <v>30.25</v>
       </c>
       <c r="L84" t="n">
-        <v>0.8572324514389038</v>
+        <v>0.8940473198890686</v>
       </c>
       <c r="M84" t="n">
         <v>5</v>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="n">
-        <v>0.6578512191772461</v>
+        <v>0.6494854688644409</v>
       </c>
       <c r="D85" t="n">
         <v>2</v>
@@ -4075,7 +4075,7 @@
         <v>7.875</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8264926075935364</v>
+        <v>0.83836829662323</v>
       </c>
       <c r="G85" t="n">
         <v>2</v>
@@ -4084,7 +4084,7 @@
         <v>4.25</v>
       </c>
       <c r="I85" t="n">
-        <v>0.7403752207756042</v>
+        <v>0.7565320730209351</v>
       </c>
       <c r="J85" t="n">
         <v>3</v>
@@ -4093,7 +4093,7 @@
         <v>19.5</v>
       </c>
       <c r="L85" t="n">
-        <v>0.798125147819519</v>
+        <v>0.7971017360687256</v>
       </c>
       <c r="M85" t="n">
         <v>5</v>
@@ -4110,7 +4110,7 @@
         <v>0.7253998517990112</v>
       </c>
       <c r="C86" t="n">
-        <v>0.6340843439102173</v>
+        <v>0.6022336483001709</v>
       </c>
       <c r="D86" t="n">
         <v>2</v>
@@ -4119,7 +4119,7 @@
         <v>5.25</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6587166786193848</v>
+        <v>0.6182465553283691</v>
       </c>
       <c r="G86" t="n">
         <v>2</v>
@@ -4128,7 +4128,7 @@
         <v>5.222222222222222</v>
       </c>
       <c r="I86" t="n">
-        <v>0.8046817779541016</v>
+        <v>0.8054541945457458</v>
       </c>
       <c r="J86" t="n">
         <v>3</v>
@@ -4137,7 +4137,7 @@
         <v>17.75</v>
       </c>
       <c r="L86" t="n">
-        <v>0.7960072159767151</v>
+        <v>0.8078435659408569</v>
       </c>
       <c r="M86" t="n">
         <v>5</v>
@@ -4154,7 +4154,7 @@
         <v>0.6843113303184509</v>
       </c>
       <c r="C87" t="n">
-        <v>0.7002801895141602</v>
+        <v>0.4453679919242859</v>
       </c>
       <c r="D87" t="n">
         <v>2</v>
@@ -4163,7 +4163,7 @@
         <v>6.875</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7978704571723938</v>
+        <v>0.7641056180000305</v>
       </c>
       <c r="G87" t="n">
         <v>2</v>
@@ -4172,7 +4172,7 @@
         <v>4.361111111111111</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7746871113777161</v>
+        <v>0.7477748394012451</v>
       </c>
       <c r="J87" t="n">
         <v>3</v>
@@ -4181,7 +4181,7 @@
         <v>25</v>
       </c>
       <c r="L87" t="n">
-        <v>0.8059327602386475</v>
+        <v>0.7784504890441895</v>
       </c>
       <c r="M87" t="n">
         <v>5</v>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0.4914684891700745</v>
+        <v>0.5143059492111206</v>
       </c>
       <c r="D88" t="n">
         <v>2</v>
@@ -4205,7 +4205,7 @@
         <v>9.875</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4706100821495056</v>
+        <v>0.5363311767578125</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -4214,7 +4214,7 @@
         <v>2.416666666666667</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7615155577659607</v>
+        <v>0.7591668367385864</v>
       </c>
       <c r="J88" t="n">
         <v>3</v>
@@ -4223,7 +4223,7 @@
         <v>30.25</v>
       </c>
       <c r="L88" t="n">
-        <v>0.8179596066474915</v>
+        <v>0.7881501317024231</v>
       </c>
       <c r="M88" t="n">
         <v>5</v>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0.630679726600647</v>
+        <v>0.6948239207267761</v>
       </c>
       <c r="D89" t="n">
         <v>2</v>
@@ -4247,7 +4247,7 @@
         <v>13.875</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5940780639648438</v>
+        <v>0.6396819353103638</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
@@ -4256,7 +4256,7 @@
         <v>2.722222222222222</v>
       </c>
       <c r="I89" t="n">
-        <v>0.841505765914917</v>
+        <v>0.8298189640045166</v>
       </c>
       <c r="J89" t="n">
         <v>3</v>
@@ -4265,7 +4265,7 @@
         <v>21.75</v>
       </c>
       <c r="L89" t="n">
-        <v>0.7089740037918091</v>
+        <v>0.7016227245330811</v>
       </c>
       <c r="M89" t="n">
         <v>5</v>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="n">
-        <v>0.5003719329833984</v>
+        <v>0.5221861004829407</v>
       </c>
       <c r="D90" t="n">
         <v>2</v>
@@ -4289,7 +4289,7 @@
         <v>7.875</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8364017009735107</v>
+        <v>0.7890506982803345</v>
       </c>
       <c r="G90" t="n">
         <v>2</v>
@@ -4298,7 +4298,7 @@
         <v>8.722222222222221</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5991138219833374</v>
+        <v>0.6006051898002625</v>
       </c>
       <c r="J90" t="n">
         <v>3</v>
@@ -4318,7 +4318,7 @@
         <v>0.6948223114013672</v>
       </c>
       <c r="C91" t="n">
-        <v>0.4732171595096588</v>
+        <v>0.4601981639862061</v>
       </c>
       <c r="D91" t="n">
         <v>3</v>
@@ -4327,7 +4327,7 @@
         <v>16.125</v>
       </c>
       <c r="F91" t="n">
-        <v>0.693861722946167</v>
+        <v>0.6830084919929504</v>
       </c>
       <c r="G91" t="n">
         <v>2</v>
@@ -4336,7 +4336,7 @@
         <v>5.916666666666667</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5624362826347351</v>
+        <v>0.5662627220153809</v>
       </c>
       <c r="J91" t="n">
         <v>3</v>
@@ -4345,7 +4345,7 @@
         <v>28.25</v>
       </c>
       <c r="L91" t="n">
-        <v>0.7978891134262085</v>
+        <v>0.7842456698417664</v>
       </c>
       <c r="M91" t="n">
         <v>5</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0.500450611114502</v>
+        <v>0.5209137201309204</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         <v>3.375</v>
       </c>
       <c r="F92" t="n">
-        <v>0.4211498200893402</v>
+        <v>0.4265526831150055</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -4378,7 +4378,7 @@
         <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4484359920024872</v>
+        <v>0.4792638719081879</v>
       </c>
       <c r="J92" t="n">
         <v>3</v>
@@ -4387,7 +4387,7 @@
         <v>16.75</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8833005428314209</v>
+        <v>0.8454389572143555</v>
       </c>
       <c r="M92" t="n">
         <v>5</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.6912092566490173</v>
+        <v>0.6812053918838501</v>
       </c>
       <c r="D93" t="n">
         <v>2</v>
@@ -4411,7 +4411,7 @@
         <v>4.25</v>
       </c>
       <c r="F93" t="n">
-        <v>0.6783744096755981</v>
+        <v>0.7004399299621582</v>
       </c>
       <c r="G93" t="n">
         <v>2</v>
@@ -4420,7 +4420,7 @@
         <v>4.638888888888889</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7133484482765198</v>
+        <v>0.6797668933868408</v>
       </c>
       <c r="J93" t="n">
         <v>3</v>
@@ -4429,7 +4429,7 @@
         <v>22.75</v>
       </c>
       <c r="L93" t="n">
-        <v>0.8305410146713257</v>
+        <v>0.8042992353439331</v>
       </c>
       <c r="M93" t="n">
         <v>5</v>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="n">
-        <v>0.7412557601928711</v>
+        <v>0.6861858367919922</v>
       </c>
       <c r="D94" t="n">
         <v>2</v>
@@ -4453,7 +4453,7 @@
         <v>10.875</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4569532871246338</v>
+        <v>0.5028095841407776</v>
       </c>
       <c r="G94" t="n">
         <v>2</v>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0.8683230876922607</v>
+        <v>0.8870812058448792</v>
       </c>
       <c r="D95" t="n">
         <v>3</v>
@@ -4483,7 +4483,7 @@
         <v>15.125</v>
       </c>
       <c r="F95" t="n">
-        <v>0.962573230266571</v>
+        <v>0.9210875034332275</v>
       </c>
       <c r="G95" t="n">
         <v>2</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0.7679597139358521</v>
+        <v>0.7913576364517212</v>
       </c>
       <c r="D96" t="n">
         <v>2</v>
@@ -4513,7 +4513,7 @@
         <v>8.125</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8576165437698364</v>
+        <v>0.8781294822692871</v>
       </c>
       <c r="G96" t="n">
         <v>2</v>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0.7078534364700317</v>
+        <v>0.6423952579498291</v>
       </c>
       <c r="D97" t="n">
         <v>3</v>
@@ -4543,7 +4543,7 @@
         <v>15.125</v>
       </c>
       <c r="F97" t="n">
-        <v>0.8192610740661621</v>
+        <v>0.925756573677063</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>0.6759837865829468</v>
+        <v>0.7571213841438293</v>
       </c>
       <c r="D98" t="n">
         <v>3</v>
@@ -4573,7 +4573,7 @@
         <v>18.375</v>
       </c>
       <c r="F98" t="n">
-        <v>0.48934406042099</v>
+        <v>0.4332346320152283</v>
       </c>
       <c r="G98" t="n">
         <v>1</v>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.6782317161560059</v>
+        <v>0.6725191473960876</v>
       </c>
       <c r="D99" t="n">
         <v>2</v>
@@ -4603,7 +4603,7 @@
         <v>8.625</v>
       </c>
       <c r="F99" t="n">
-        <v>0.9251835942268372</v>
+        <v>0.9332767724990845</v>
       </c>
       <c r="G99" t="n">
         <v>3</v>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0.8012504577636719</v>
+        <v>0.8200989961624146</v>
       </c>
       <c r="D100" t="n">
         <v>3</v>
@@ -4633,7 +4633,7 @@
         <v>16.625</v>
       </c>
       <c r="F100" t="n">
-        <v>0.894376277923584</v>
+        <v>0.890754222869873</v>
       </c>
       <c r="G100" t="n">
         <v>2</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.7709678411483765</v>
+        <v>0.7792035341262817</v>
       </c>
       <c r="D101" t="n">
         <v>2</v>
@@ -4663,7 +4663,7 @@
         <v>7</v>
       </c>
       <c r="F101" t="n">
-        <v>0.8639695644378662</v>
+        <v>0.8413156270980835</v>
       </c>
       <c r="G101" t="n">
         <v>2</v>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>0.72697913646698</v>
+        <v>0.689461350440979</v>
       </c>
       <c r="D102" t="n">
         <v>2</v>
@@ -4693,7 +4693,7 @@
         <v>9.125</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8176989555358887</v>
+        <v>0.8132539987564087</v>
       </c>
       <c r="G102" t="n">
         <v>2</v>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="n">
-        <v>0.5342023372650146</v>
+        <v>0.5500186681747437</v>
       </c>
       <c r="D103" t="n">
         <v>2</v>
@@ -4723,7 +4723,7 @@
         <v>5.125</v>
       </c>
       <c r="F103" t="n">
-        <v>0.8821453452110291</v>
+        <v>0.8812790513038635</v>
       </c>
       <c r="G103" t="n">
         <v>2</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>0.3997960388660431</v>
+        <v>0.4076334536075592</v>
       </c>
       <c r="D104" t="n">
         <v>2</v>
@@ -4753,7 +4753,7 @@
         <v>8</v>
       </c>
       <c r="F104" t="n">
-        <v>0.7772665023803711</v>
+        <v>0.8013513088226318</v>
       </c>
       <c r="G104" t="n">
         <v>2</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>0.5718060731887817</v>
+        <v>0.6071251630783081</v>
       </c>
       <c r="D105" t="n">
         <v>2</v>
@@ -4783,7 +4783,7 @@
         <v>8.25</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7982349395751953</v>
+        <v>0.7893891930580139</v>
       </c>
       <c r="G105" t="n">
         <v>2</v>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>0.5739610195159912</v>
+        <v>0.5541701316833496</v>
       </c>
       <c r="D106" t="n">
         <v>2</v>
@@ -4813,7 +4813,7 @@
         <v>8.75</v>
       </c>
       <c r="F106" t="n">
-        <v>0.7639610767364502</v>
+        <v>0.7529270648956299</v>
       </c>
       <c r="G106" t="n">
         <v>2</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="n">
-        <v>0.6306372880935669</v>
+        <v>0.5939823389053345</v>
       </c>
       <c r="D107" t="n">
         <v>2</v>
@@ -4843,7 +4843,7 @@
         <v>10.5</v>
       </c>
       <c r="F107" t="n">
-        <v>0.8626648187637329</v>
+        <v>0.8384395837783813</v>
       </c>
       <c r="G107" t="n">
         <v>2</v>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>0.7215304374694824</v>
+        <v>0.7033221125602722</v>
       </c>
       <c r="D108" t="n">
         <v>2</v>
@@ -4873,7 +4873,7 @@
         <v>9.375</v>
       </c>
       <c r="F108" t="n">
-        <v>0.7937959432601929</v>
+        <v>0.7424035668373108</v>
       </c>
       <c r="G108" t="n">
         <v>2</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>0.5659373998641968</v>
+        <v>0.6962581872940063</v>
       </c>
       <c r="D109" t="n">
         <v>3</v>
@@ -4903,7 +4903,7 @@
         <v>21</v>
       </c>
       <c r="F109" t="n">
-        <v>0.790616512298584</v>
+        <v>0.8069183826446533</v>
       </c>
       <c r="G109" t="n">
         <v>2</v>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>0.6038139462471008</v>
+        <v>0.5886511206626892</v>
       </c>
       <c r="D110" t="n">
         <v>2</v>
@@ -4933,7 +4933,7 @@
         <v>4.75</v>
       </c>
       <c r="F110" t="n">
-        <v>0.7235755920410156</v>
+        <v>0.6771970987319946</v>
       </c>
       <c r="G110" t="n">
         <v>1</v>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>0.5507063865661621</v>
+        <v>0.5848898887634277</v>
       </c>
       <c r="D111" t="n">
         <v>2</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>0.8775882720947266</v>
+        <v>0.8438047170639038</v>
       </c>
       <c r="D112" t="n">
         <v>3</v>
@@ -4991,7 +4991,7 @@
         <v>19.375</v>
       </c>
       <c r="F112" t="n">
-        <v>0.8772934675216675</v>
+        <v>0.8753972053527832</v>
       </c>
       <c r="G112" t="n">
         <v>2</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>0.9566200971603394</v>
+        <v>0.9639600515365601</v>
       </c>
       <c r="D113" t="n">
         <v>2</v>
@@ -5021,7 +5021,7 @@
         <v>12.625</v>
       </c>
       <c r="F113" t="n">
-        <v>0.7763075828552246</v>
+        <v>0.7486721277236938</v>
       </c>
       <c r="G113" t="n">
         <v>2</v>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="n">
-        <v>0.7332712411880493</v>
+        <v>0.7896417379379272</v>
       </c>
       <c r="D114" t="n">
         <v>3</v>
@@ -5051,7 +5051,7 @@
         <v>26</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7218976616859436</v>
+        <v>0.7910975813865662</v>
       </c>
       <c r="G114" t="n">
         <v>2</v>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
-        <v>0.5609755516052246</v>
+        <v>0.5330381989479065</v>
       </c>
       <c r="D115" t="n">
         <v>2</v>
@@ -5081,7 +5081,7 @@
         <v>5</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6607449054718018</v>
+        <v>0.6635669469833374</v>
       </c>
       <c r="G115" t="n">
         <v>2</v>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>0.5920734405517578</v>
+        <v>0.5923558473587036</v>
       </c>
       <c r="D116" t="n">
         <v>2</v>
@@ -5111,7 +5111,7 @@
         <v>8.25</v>
       </c>
       <c r="F116" t="n">
-        <v>0.8719115257263184</v>
+        <v>0.9050606489181519</v>
       </c>
       <c r="G116" t="n">
         <v>2</v>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>0.6323555111885071</v>
+        <v>0.6168935298919678</v>
       </c>
       <c r="D117" t="n">
         <v>2</v>
@@ -5141,7 +5141,7 @@
         <v>10</v>
       </c>
       <c r="F117" t="n">
-        <v>0.8993455767631531</v>
+        <v>0.8778447508811951</v>
       </c>
       <c r="G117" t="n">
         <v>3</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="n">
-        <v>0.3581017255783081</v>
+        <v>0.2399159669876099</v>
       </c>
       <c r="D118" t="n">
         <v>2</v>
@@ -5171,7 +5171,7 @@
         <v>7.125</v>
       </c>
       <c r="F118" t="n">
-        <v>0.6251416802406311</v>
+        <v>0.6395949721336365</v>
       </c>
       <c r="G118" t="n">
         <v>1</v>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>0.5575861930847168</v>
+        <v>0.6100476980209351</v>
       </c>
       <c r="D119" t="n">
         <v>2</v>
@@ -5201,7 +5201,7 @@
         <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5927873849868774</v>
+        <v>0.5908904671669006</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -5224,7 +5224,7 @@
         <v>0.6694537997245789</v>
       </c>
       <c r="C120" t="n">
-        <v>0.3698970675468445</v>
+        <v>0.3681106269359589</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -5233,7 +5233,7 @@
         <v>2.625</v>
       </c>
       <c r="F120" t="n">
-        <v>0.9320868253707886</v>
+        <v>0.9337451457977295</v>
       </c>
       <c r="G120" t="n">
         <v>3</v>
@@ -5242,7 +5242,7 @@
         <v>14.25</v>
       </c>
       <c r="I120" t="n">
-        <v>0.5754612684249878</v>
+        <v>0.540064811706543</v>
       </c>
       <c r="J120" t="n">
         <v>2</v>
@@ -5251,7 +5251,7 @@
         <v>12.25</v>
       </c>
       <c r="L120" t="n">
-        <v>0.736781120300293</v>
+        <v>0.7337006330490112</v>
       </c>
       <c r="M120" t="n">
         <v>5</v>
@@ -5268,7 +5268,7 @@
         <v>0.6708939075469971</v>
       </c>
       <c r="C121" t="n">
-        <v>0.6328518986701965</v>
+        <v>0.6787805557250977</v>
       </c>
       <c r="D121" t="n">
         <v>2</v>
@@ -5277,7 +5277,7 @@
         <v>12.5</v>
       </c>
       <c r="F121" t="n">
-        <v>0.8666946887969971</v>
+        <v>0.8741277456283569</v>
       </c>
       <c r="G121" t="n">
         <v>3</v>
@@ -5286,7 +5286,7 @@
         <v>20</v>
       </c>
       <c r="I121" t="n">
-        <v>0.6670637130737305</v>
+        <v>0.6731353998184204</v>
       </c>
       <c r="J121" t="n">
         <v>3</v>
@@ -5295,7 +5295,7 @@
         <v>23.25</v>
       </c>
       <c r="L121" t="n">
-        <v>0.7381026744842529</v>
+        <v>0.7542791366577148</v>
       </c>
       <c r="M121" t="n">
         <v>5</v>
@@ -5312,7 +5312,7 @@
         <v>0.7633491158485413</v>
       </c>
       <c r="C122" t="n">
-        <v>0.8459526300430298</v>
+        <v>0.8434574604034424</v>
       </c>
       <c r="D122" t="n">
         <v>3</v>
@@ -5321,7 +5321,7 @@
         <v>19.625</v>
       </c>
       <c r="F122" t="n">
-        <v>0.7036791443824768</v>
+        <v>0.7205095291137695</v>
       </c>
       <c r="G122" t="n">
         <v>2</v>
@@ -5330,7 +5330,7 @@
         <v>4.888888888888889</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8530491590499878</v>
+        <v>0.8683103919029236</v>
       </c>
       <c r="J122" t="n">
         <v>3</v>
@@ -5339,7 +5339,7 @@
         <v>34.25</v>
       </c>
       <c r="L122" t="n">
-        <v>0.79527747631073</v>
+        <v>0.8106295466423035</v>
       </c>
       <c r="M122" t="n">
         <v>5</v>
@@ -5356,7 +5356,7 @@
         <v>0.7070568799972534</v>
       </c>
       <c r="C123" t="n">
-        <v>0.8860903382301331</v>
+        <v>0.9012067914009094</v>
       </c>
       <c r="D123" t="n">
         <v>2</v>
@@ -5365,7 +5365,7 @@
         <v>10.25</v>
       </c>
       <c r="F123" t="n">
-        <v>0.865212619304657</v>
+        <v>0.9174085259437561</v>
       </c>
       <c r="G123" t="n">
         <v>2</v>
@@ -5374,7 +5374,7 @@
         <v>8.083333333333334</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8546127080917358</v>
+        <v>0.8391269445419312</v>
       </c>
       <c r="J123" t="n">
         <v>3</v>
@@ -5383,7 +5383,7 @@
         <v>24</v>
       </c>
       <c r="L123" t="n">
-        <v>0.7366674542427063</v>
+        <v>0.7368403077125549</v>
       </c>
       <c r="M123" t="n">
         <v>5</v>
@@ -5405,7 +5405,7 @@
         <v>5.125</v>
       </c>
       <c r="F124" t="n">
-        <v>0.8623640537261963</v>
+        <v>0.9004160165786743</v>
       </c>
       <c r="G124" t="n">
         <v>3</v>
@@ -5414,7 +5414,7 @@
         <v>16.47222222222222</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7659975290298462</v>
+        <v>0.7503265142440796</v>
       </c>
       <c r="J124" t="n">
         <v>3</v>
@@ -5423,7 +5423,7 @@
         <v>25.5</v>
       </c>
       <c r="L124" t="n">
-        <v>0.7795952558517456</v>
+        <v>0.7621227502822876</v>
       </c>
       <c r="M124" t="n">
         <v>5</v>
@@ -5447,7 +5447,7 @@
         <v>3.5</v>
       </c>
       <c r="F125" t="n">
-        <v>0.5619850158691406</v>
+        <v>0.5725111961364746</v>
       </c>
       <c r="G125" t="n">
         <v>2</v>
@@ -5456,7 +5456,7 @@
         <v>4.027777777777778</v>
       </c>
       <c r="I125" t="n">
-        <v>0.7791652679443359</v>
+        <v>0.8810018301010132</v>
       </c>
       <c r="J125" t="n">
         <v>3</v>
@@ -5465,7 +5465,7 @@
         <v>30.5</v>
       </c>
       <c r="L125" t="n">
-        <v>0.7522549629211426</v>
+        <v>0.7248208522796631</v>
       </c>
       <c r="M125" t="n">
         <v>5</v>
@@ -5482,7 +5482,7 @@
         <v>0.7075763940811157</v>
       </c>
       <c r="C126" t="n">
-        <v>1.000000238418579</v>
+        <v>1.00000011920929</v>
       </c>
       <c r="D126" t="n">
         <v>2</v>
@@ -5491,7 +5491,7 @@
         <v>13.375</v>
       </c>
       <c r="F126" t="n">
-        <v>0.7973366975784302</v>
+        <v>0.7697989940643311</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -5500,7 +5500,7 @@
         <v>3.722222222222222</v>
       </c>
       <c r="I126" t="n">
-        <v>0.711825966835022</v>
+        <v>0.7559051513671875</v>
       </c>
       <c r="J126" t="n">
         <v>3</v>
@@ -5509,7 +5509,7 @@
         <v>23.25</v>
       </c>
       <c r="L126" t="n">
-        <v>0.7672242522239685</v>
+        <v>0.7166860103607178</v>
       </c>
       <c r="M126" t="n">
         <v>5</v>
@@ -5526,7 +5526,7 @@
         <v>0.7552201747894287</v>
       </c>
       <c r="C127" t="n">
-        <v>0.7488197088241577</v>
+        <v>0.8121333718299866</v>
       </c>
       <c r="D127" t="n">
         <v>3</v>
@@ -5535,7 +5535,7 @@
         <v>18.375</v>
       </c>
       <c r="F127" t="n">
-        <v>0.8736200928688049</v>
+        <v>0.8908710479736328</v>
       </c>
       <c r="G127" t="n">
         <v>2</v>
@@ -5544,7 +5544,7 @@
         <v>6.222222222222222</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8228620290756226</v>
+        <v>0.847551167011261</v>
       </c>
       <c r="J127" t="n">
         <v>3</v>
@@ -5553,7 +5553,7 @@
         <v>36</v>
       </c>
       <c r="L127" t="n">
-        <v>0.8282395601272583</v>
+        <v>0.8109331130981445</v>
       </c>
       <c r="M127" t="n">
         <v>5</v>
@@ -5570,7 +5570,7 @@
         <v>0.7783278226852417</v>
       </c>
       <c r="C128" t="n">
-        <v>0.6938724517822266</v>
+        <v>0.7188695073127747</v>
       </c>
       <c r="D128" t="n">
         <v>2</v>
@@ -5579,7 +5579,7 @@
         <v>9.25</v>
       </c>
       <c r="F128" t="n">
-        <v>0.9080865383148193</v>
+        <v>0.9183028340339661</v>
       </c>
       <c r="G128" t="n">
         <v>3</v>
@@ -5588,7 +5588,7 @@
         <v>14.36111111111111</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7998548150062561</v>
+        <v>0.8673692345619202</v>
       </c>
       <c r="J128" t="n">
         <v>3</v>
@@ -5597,7 +5597,7 @@
         <v>34.25</v>
       </c>
       <c r="L128" t="n">
-        <v>0.564638614654541</v>
+        <v>0.6152557134628296</v>
       </c>
       <c r="M128" t="n">
         <v>5</v>
@@ -5614,7 +5614,7 @@
         <v>0.6672012805938721</v>
       </c>
       <c r="C129" t="n">
-        <v>0.6980853080749512</v>
+        <v>0.7200015783309937</v>
       </c>
       <c r="D129" t="n">
         <v>2</v>
@@ -5623,7 +5623,7 @@
         <v>13.875</v>
       </c>
       <c r="F129" t="n">
-        <v>0.8002035617828369</v>
+        <v>0.8125752210617065</v>
       </c>
       <c r="G129" t="n">
         <v>2</v>
@@ -5632,7 +5632,7 @@
         <v>5.472222222222222</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8285601735115051</v>
+        <v>0.8259938955307007</v>
       </c>
       <c r="J129" t="n">
         <v>3</v>
@@ -5641,7 +5641,7 @@
         <v>36.5</v>
       </c>
       <c r="L129" t="n">
-        <v>0.7067480087280273</v>
+        <v>0.6861435174942017</v>
       </c>
       <c r="M129" t="n">
         <v>5</v>
@@ -5658,7 +5658,7 @@
         <v>0.710345983505249</v>
       </c>
       <c r="C130" t="n">
-        <v>0.5522591471672058</v>
+        <v>0.5374878644943237</v>
       </c>
       <c r="D130" t="n">
         <v>3</v>
@@ -5667,7 +5667,7 @@
         <v>17.125</v>
       </c>
       <c r="F130" t="n">
-        <v>0.8409625291824341</v>
+        <v>0.8697942495346069</v>
       </c>
       <c r="G130" t="n">
         <v>2</v>
@@ -5676,7 +5676,7 @@
         <v>9.694444444444445</v>
       </c>
       <c r="I130" t="n">
-        <v>0.8373373746871948</v>
+        <v>0.823480486869812</v>
       </c>
       <c r="J130" t="n">
         <v>3</v>
@@ -5685,7 +5685,7 @@
         <v>41</v>
       </c>
       <c r="L130" t="n">
-        <v>0.732828676700592</v>
+        <v>0.7442566156387329</v>
       </c>
       <c r="M130" t="n">
         <v>5</v>
@@ -5702,7 +5702,7 @@
         <v>0.7156832814216614</v>
       </c>
       <c r="C131" t="n">
-        <v>0.8277767300605774</v>
+        <v>0.8164983987808228</v>
       </c>
       <c r="D131" t="n">
         <v>3</v>
@@ -5711,7 +5711,7 @@
         <v>15.5</v>
       </c>
       <c r="F131" t="n">
-        <v>0.7685868740081787</v>
+        <v>0.7785782814025879</v>
       </c>
       <c r="G131" t="n">
         <v>2</v>
@@ -5720,7 +5720,7 @@
         <v>7.555555555555555</v>
       </c>
       <c r="I131" t="n">
-        <v>0.7024664878845215</v>
+        <v>0.7685495615005493</v>
       </c>
       <c r="J131" t="n">
         <v>3</v>
@@ -5729,7 +5729,7 @@
         <v>33.75</v>
       </c>
       <c r="L131" t="n">
-        <v>0.7104842662811279</v>
+        <v>0.6434782743453979</v>
       </c>
       <c r="M131" t="n">
         <v>5</v>
@@ -5746,7 +5746,7 @@
         <v>0.7081096172332764</v>
       </c>
       <c r="C132" t="n">
-        <v>0.7880979776382446</v>
+        <v>0.7956169247627258</v>
       </c>
       <c r="D132" t="n">
         <v>2</v>
@@ -5755,7 +5755,7 @@
         <v>6.75</v>
       </c>
       <c r="F132" t="n">
-        <v>0.8239110708236694</v>
+        <v>0.8378271460533142</v>
       </c>
       <c r="G132" t="n">
         <v>2</v>
@@ -5764,7 +5764,7 @@
         <v>5.083333333333333</v>
       </c>
       <c r="I132" t="n">
-        <v>0.707808792591095</v>
+        <v>0.6673024296760559</v>
       </c>
       <c r="J132" t="n">
         <v>3</v>
@@ -5773,7 +5773,7 @@
         <v>32</v>
       </c>
       <c r="L132" t="n">
-        <v>0.6884533166885376</v>
+        <v>0.6881400346755981</v>
       </c>
       <c r="M132" t="n">
         <v>5</v>
@@ -5797,7 +5797,7 @@
         <v>1.25</v>
       </c>
       <c r="F133" t="n">
-        <v>0.7787646651268005</v>
+        <v>0.8077818751335144</v>
       </c>
       <c r="G133" t="n">
         <v>2</v>
@@ -5806,7 +5806,7 @@
         <v>8.083333333333334</v>
       </c>
       <c r="I133" t="n">
-        <v>0.7663620710372925</v>
+        <v>0.7407582998275757</v>
       </c>
       <c r="J133" t="n">
         <v>3</v>
@@ -5815,7 +5815,7 @@
         <v>28.5</v>
       </c>
       <c r="L133" t="n">
-        <v>0.4767873585224152</v>
+        <v>0.5314902067184448</v>
       </c>
       <c r="M133" t="n">
         <v>5</v>
@@ -5832,7 +5832,7 @@
         <v>0.7367768287658691</v>
       </c>
       <c r="C134" t="n">
-        <v>0.7557097673416138</v>
+        <v>0.7294521331787109</v>
       </c>
       <c r="D134" t="n">
         <v>2</v>
@@ -5841,7 +5841,7 @@
         <v>10.75</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6292126178741455</v>
+        <v>0.699280858039856</v>
       </c>
       <c r="G134" t="n">
         <v>2</v>
@@ -5850,7 +5850,7 @@
         <v>4.416666666666667</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6859351396560669</v>
+        <v>0.6884915232658386</v>
       </c>
       <c r="J134" t="n">
         <v>3</v>
@@ -5859,7 +5859,7 @@
         <v>26.75</v>
       </c>
       <c r="L134" t="n">
-        <v>0.7266452312469482</v>
+        <v>0.7355816960334778</v>
       </c>
       <c r="M134" t="n">
         <v>5</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>0.9999998807907104</v>
       </c>
       <c r="D135" t="n">
         <v>3</v>
@@ -5883,7 +5883,7 @@
         <v>20.625</v>
       </c>
       <c r="F135" t="n">
-        <v>0.5661180019378662</v>
+        <v>0.5855114459991455</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -5892,7 +5892,7 @@
         <v>2.555555555555555</v>
       </c>
       <c r="I135" t="n">
-        <v>0.6961175203323364</v>
+        <v>0.7480537295341492</v>
       </c>
       <c r="J135" t="n">
         <v>3</v>
@@ -5901,7 +5901,7 @@
         <v>30.75</v>
       </c>
       <c r="L135" t="n">
-        <v>0.6748595237731934</v>
+        <v>0.7056179046630859</v>
       </c>
       <c r="M135" t="n">
         <v>5</v>
@@ -5918,7 +5918,7 @@
         <v>0.7328077554702759</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4853947162628174</v>
+        <v>0.5107315182685852</v>
       </c>
       <c r="D136" t="n">
         <v>2</v>
@@ -5927,7 +5927,7 @@
         <v>9.75</v>
       </c>
       <c r="F136" t="n">
-        <v>0.7668032646179199</v>
+        <v>0.7484309673309326</v>
       </c>
       <c r="G136" t="n">
         <v>2</v>
@@ -5936,7 +5936,7 @@
         <v>5.277777777777778</v>
       </c>
       <c r="I136" t="n">
-        <v>0.6643783450126648</v>
+        <v>0.6136960983276367</v>
       </c>
       <c r="J136" t="n">
         <v>3</v>
@@ -5945,7 +5945,7 @@
         <v>33.5</v>
       </c>
       <c r="L136" t="n">
-        <v>0.7336738109588623</v>
+        <v>0.708422064781189</v>
       </c>
       <c r="M136" t="n">
         <v>5</v>
@@ -5962,7 +5962,7 @@
         <v>0.6929190158843994</v>
       </c>
       <c r="C137" t="n">
-        <v>0.6926129460334778</v>
+        <v>0.7363888621330261</v>
       </c>
       <c r="D137" t="n">
         <v>2</v>
@@ -5971,7 +5971,7 @@
         <v>4.875</v>
       </c>
       <c r="F137" t="n">
-        <v>0.769172191619873</v>
+        <v>0.7256118059158325</v>
       </c>
       <c r="G137" t="n">
         <v>2</v>
@@ -5980,7 +5980,7 @@
         <v>6.333333333333333</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7399228811264038</v>
+        <v>0.8325875401496887</v>
       </c>
       <c r="J137" t="n">
         <v>3</v>
@@ -5989,7 +5989,7 @@
         <v>36.5</v>
       </c>
       <c r="L137" t="n">
-        <v>0.7122310400009155</v>
+        <v>0.7073348760604858</v>
       </c>
       <c r="M137" t="n">
         <v>5</v>
@@ -6006,7 +6006,7 @@
         <v>0.3634530305862427</v>
       </c>
       <c r="C138" t="n">
-        <v>0.6646533012390137</v>
+        <v>0.5870909690856934</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
@@ -6015,7 +6015,7 @@
         <v>3.75</v>
       </c>
       <c r="F138" t="n">
-        <v>0.7599273920059204</v>
+        <v>0.7658042311668396</v>
       </c>
       <c r="G138" t="n">
         <v>2</v>
@@ -6024,7 +6024,7 @@
         <v>5.805555555555555</v>
       </c>
       <c r="I138" t="n">
-        <v>0.7778961658477783</v>
+        <v>0.6290267705917358</v>
       </c>
       <c r="J138" t="n">
         <v>3</v>
@@ -6033,7 +6033,7 @@
         <v>19</v>
       </c>
       <c r="L138" t="n">
-        <v>0.6935513615608215</v>
+        <v>0.6539986133575439</v>
       </c>
       <c r="M138" t="n">
         <v>5</v>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>0.7565690279006958</v>
+        <v>0.7363743782043457</v>
       </c>
       <c r="D139" t="n">
         <v>2</v>
@@ -6060,7 +6060,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
-        <v>0.7512275576591492</v>
+        <v>0.7668627500534058</v>
       </c>
       <c r="J139" t="n">
         <v>3</v>
@@ -6069,7 +6069,7 @@
         <v>40.75</v>
       </c>
       <c r="L139" t="n">
-        <v>0.7564536333084106</v>
+        <v>0.7450953125953674</v>
       </c>
       <c r="M139" t="n">
         <v>5</v>
@@ -6086,7 +6086,7 @@
         <v>0.7038396596908569</v>
       </c>
       <c r="C140" t="n">
-        <v>0.775701642036438</v>
+        <v>0.7492239475250244</v>
       </c>
       <c r="D140" t="n">
         <v>2</v>
@@ -6102,7 +6102,7 @@
         <v>1.166666666666667</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7888789176940918</v>
+        <v>0.7354633212089539</v>
       </c>
       <c r="J140" t="n">
         <v>3</v>
@@ -6111,7 +6111,7 @@
         <v>32.25</v>
       </c>
       <c r="L140" t="n">
-        <v>0.6756742000579834</v>
+        <v>0.6922202110290527</v>
       </c>
       <c r="M140" t="n">
         <v>5</v>
@@ -6128,7 +6128,7 @@
         <v>0.6824962496757507</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5543227791786194</v>
+        <v>0.5670887231826782</v>
       </c>
       <c r="D141" t="n">
         <v>2</v>
@@ -6137,7 +6137,7 @@
         <v>10</v>
       </c>
       <c r="F141" t="n">
-        <v>0.6689144372940063</v>
+        <v>0.6704363226890564</v>
       </c>
       <c r="G141" t="n">
         <v>2</v>
@@ -6146,7 +6146,7 @@
         <v>7</v>
       </c>
       <c r="I141" t="n">
-        <v>0.7876960635185242</v>
+        <v>0.8498623967170715</v>
       </c>
       <c r="J141" t="n">
         <v>3</v>
@@ -6155,7 +6155,7 @@
         <v>40.75</v>
       </c>
       <c r="L141" t="n">
-        <v>0.5680205821990967</v>
+        <v>0.5907394886016846</v>
       </c>
       <c r="M141" t="n">
         <v>5</v>
@@ -6172,7 +6172,7 @@
         <v>0.6950209140777588</v>
       </c>
       <c r="C142" t="n">
-        <v>0.7027095556259155</v>
+        <v>0.721920371055603</v>
       </c>
       <c r="D142" t="n">
         <v>2</v>
@@ -6181,7 +6181,7 @@
         <v>4.125</v>
       </c>
       <c r="F142" t="n">
-        <v>0.7825068831443787</v>
+        <v>0.7484210729598999</v>
       </c>
       <c r="G142" t="n">
         <v>2</v>
@@ -6190,7 +6190,7 @@
         <v>5.638888888888889</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7850190401077271</v>
+        <v>0.7380591630935669</v>
       </c>
       <c r="J142" t="n">
         <v>3</v>
@@ -6199,7 +6199,7 @@
         <v>28.75</v>
       </c>
       <c r="L142" t="n">
-        <v>0.7145567536354065</v>
+        <v>0.7270462512969971</v>
       </c>
       <c r="M142" t="n">
         <v>5</v>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>0.578090488910675</v>
+        <v>0.5839409828186035</v>
       </c>
       <c r="D143" t="n">
         <v>2</v>
@@ -6223,7 +6223,7 @@
         <v>6.625</v>
       </c>
       <c r="F143" t="n">
-        <v>0.8415106534957886</v>
+        <v>0.8481958508491516</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -6232,7 +6232,7 @@
         <v>2.722222222222222</v>
       </c>
       <c r="I143" t="n">
-        <v>0.7747011184692383</v>
+        <v>0.7617819905281067</v>
       </c>
       <c r="J143" t="n">
         <v>3</v>
@@ -6241,7 +6241,7 @@
         <v>27.5</v>
       </c>
       <c r="L143" t="n">
-        <v>0.7332358360290527</v>
+        <v>0.6992375254631042</v>
       </c>
       <c r="M143" t="n">
         <v>5</v>
@@ -6258,7 +6258,7 @@
         <v>0.7317614555358887</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6859299540519714</v>
+        <v>0.7656728029251099</v>
       </c>
       <c r="D144" t="n">
         <v>2</v>
@@ -6267,7 +6267,7 @@
         <v>8.625</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6638814210891724</v>
+        <v>0.6742433309555054</v>
       </c>
       <c r="G144" t="n">
         <v>1</v>
@@ -6276,7 +6276,7 @@
         <v>3.333333333333333</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7557857036590576</v>
+        <v>0.7944536805152893</v>
       </c>
       <c r="J144" t="n">
         <v>3</v>
@@ -6285,7 +6285,7 @@
         <v>22.75</v>
       </c>
       <c r="L144" t="n">
-        <v>0.6942285299301147</v>
+        <v>0.6582503318786621</v>
       </c>
       <c r="M144" t="n">
         <v>5</v>
@@ -6302,7 +6302,7 @@
         <v>0.7315549254417419</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6409748792648315</v>
+        <v>0.6437852382659912</v>
       </c>
       <c r="D145" t="n">
         <v>2</v>
@@ -6311,7 +6311,7 @@
         <v>8.875</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7472014427185059</v>
+        <v>0.7349671125411987</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -6320,7 +6320,7 @@
         <v>3</v>
       </c>
       <c r="I145" t="n">
-        <v>0.6378717422485352</v>
+        <v>0.6441500782966614</v>
       </c>
       <c r="J145" t="n">
         <v>3</v>
@@ -6329,7 +6329,7 @@
         <v>28.25</v>
       </c>
       <c r="L145" t="n">
-        <v>0.5123750567436218</v>
+        <v>0.5007270574569702</v>
       </c>
       <c r="M145" t="n">
         <v>5</v>
@@ -6346,7 +6346,7 @@
         <v>0.6844040155410767</v>
       </c>
       <c r="C146" t="n">
-        <v>0.349338173866272</v>
+        <v>0.4048334360122681</v>
       </c>
       <c r="D146" t="n">
         <v>2</v>
@@ -6355,7 +6355,7 @@
         <v>5</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7540214657783508</v>
+        <v>0.7681796550750732</v>
       </c>
       <c r="G146" t="n">
         <v>1</v>
@@ -6364,7 +6364,7 @@
         <v>1.694444444444444</v>
       </c>
       <c r="I146" t="n">
-        <v>0.6698673963546753</v>
+        <v>0.6700152158737183</v>
       </c>
       <c r="J146" t="n">
         <v>3</v>
@@ -6373,7 +6373,7 @@
         <v>23.5</v>
       </c>
       <c r="L146" t="n">
-        <v>0.6982858180999756</v>
+        <v>0.7049425840377808</v>
       </c>
       <c r="M146" t="n">
         <v>5</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>0.6188170909881592</v>
+        <v>0.6205687522888184</v>
       </c>
       <c r="D147" t="n">
         <v>3</v>
@@ -6397,7 +6397,7 @@
         <v>14.375</v>
       </c>
       <c r="F147" t="n">
-        <v>0.709985613822937</v>
+        <v>0.7376847267150879</v>
       </c>
       <c r="G147" t="n">
         <v>1</v>
@@ -6406,7 +6406,7 @@
         <v>2.444444444444445</v>
       </c>
       <c r="I147" t="n">
-        <v>0.6126221418380737</v>
+        <v>0.634150505065918</v>
       </c>
       <c r="J147" t="n">
         <v>2</v>
@@ -6415,7 +6415,7 @@
         <v>13.75</v>
       </c>
       <c r="L147" t="n">
-        <v>0.6671911478042603</v>
+        <v>0.6800688505172729</v>
       </c>
       <c r="M147" t="n">
         <v>5</v>
@@ -6432,7 +6432,7 @@
         <v>0.6412843465805054</v>
       </c>
       <c r="C148" t="n">
-        <v>0.748405396938324</v>
+        <v>0.7899272441864014</v>
       </c>
       <c r="D148" t="n">
         <v>2</v>
@@ -6441,7 +6441,7 @@
         <v>7.125</v>
       </c>
       <c r="F148" t="n">
-        <v>0.9345546364784241</v>
+        <v>0.9262411594390869</v>
       </c>
       <c r="G148" t="n">
         <v>2</v>
@@ -6450,7 +6450,7 @@
         <v>5.75</v>
       </c>
       <c r="I148" t="n">
-        <v>0.700752854347229</v>
+        <v>0.7001290321350098</v>
       </c>
       <c r="J148" t="n">
         <v>3</v>
@@ -6459,7 +6459,7 @@
         <v>27.25</v>
       </c>
       <c r="L148" t="n">
-        <v>0.7035133838653564</v>
+        <v>0.7273455262184143</v>
       </c>
       <c r="M148" t="n">
         <v>5</v>
@@ -6476,7 +6476,7 @@
         <v>0.6542466282844543</v>
       </c>
       <c r="C149" t="n">
-        <v>0.6432008147239685</v>
+        <v>0.6044079065322876</v>
       </c>
       <c r="D149" t="n">
         <v>3</v>
@@ -6485,7 +6485,7 @@
         <v>29.75</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5093504786491394</v>
+        <v>0.4952409267425537</v>
       </c>
       <c r="G149" t="n">
         <v>1</v>
@@ -6494,7 +6494,7 @@
         <v>3.083333333333333</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8000622391700745</v>
+        <v>0.7754437923431396</v>
       </c>
       <c r="J149" t="n">
         <v>3</v>
@@ -6503,7 +6503,7 @@
         <v>19.25</v>
       </c>
       <c r="L149" t="n">
-        <v>0.7865796089172363</v>
+        <v>0.7656350135803223</v>
       </c>
       <c r="M149" t="n">
         <v>5</v>
@@ -6523,7 +6523,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="n">
-        <v>0.679859459400177</v>
+        <v>0.6514958739280701</v>
       </c>
       <c r="G150" t="n">
         <v>1</v>
@@ -6532,7 +6532,7 @@
         <v>2.805555555555555</v>
       </c>
       <c r="I150" t="n">
-        <v>0.7702606916427612</v>
+        <v>0.7466815114021301</v>
       </c>
       <c r="J150" t="n">
         <v>3</v>
@@ -6541,7 +6541,7 @@
         <v>28.5</v>
       </c>
       <c r="L150" t="n">
-        <v>0.8745760917663574</v>
+        <v>0.8747113943099976</v>
       </c>
       <c r="M150" t="n">
         <v>5</v>
@@ -6564,7 +6564,7 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>0.4598566591739655</v>
+        <v>0.4771811962127686</v>
       </c>
       <c r="J151" t="n">
         <v>3</v>
@@ -6573,7 +6573,7 @@
         <v>14.25</v>
       </c>
       <c r="L151" t="n">
-        <v>0.5971336364746094</v>
+        <v>0.5582867860794067</v>
       </c>
       <c r="M151" t="n">
         <v>5</v>
@@ -6596,7 +6596,7 @@
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>0.4653689861297607</v>
+        <v>0.5080028772354126</v>
       </c>
       <c r="J152" t="n">
         <v>3</v>
@@ -6605,7 +6605,7 @@
         <v>32.5</v>
       </c>
       <c r="L152" t="n">
-        <v>0.8492175340652466</v>
+        <v>0.8229652643203735</v>
       </c>
       <c r="M152" t="n">
         <v>5</v>
@@ -6628,7 +6628,7 @@
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>0.4742042422294617</v>
+        <v>0.5064139366149902</v>
       </c>
       <c r="J153" t="n">
         <v>3</v>
@@ -6637,7 +6637,7 @@
         <v>26.75</v>
       </c>
       <c r="L153" t="n">
-        <v>0.2750939130783081</v>
+        <v>0.2319312244653702</v>
       </c>
       <c r="M153" t="n">
         <v>5</v>
@@ -6660,7 +6660,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="n">
-        <v>0.8264512419700623</v>
+        <v>0.8407114148139954</v>
       </c>
       <c r="J154" t="n">
         <v>3</v>
@@ -6669,7 +6669,7 @@
         <v>26</v>
       </c>
       <c r="L154" t="n">
-        <v>0.682830810546875</v>
+        <v>0.6107555627822876</v>
       </c>
       <c r="M154" t="n">
         <v>5</v>
@@ -6692,7 +6692,7 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>0.8162448406219482</v>
+        <v>0.8428019285202026</v>
       </c>
       <c r="J155" t="n">
         <v>3</v>
@@ -6701,7 +6701,7 @@
         <v>24.75</v>
       </c>
       <c r="L155" t="n">
-        <v>0.7150863409042358</v>
+        <v>0.7334977388381958</v>
       </c>
       <c r="M155" t="n">
         <v>5</v>
@@ -6722,7 +6722,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="n">
-        <v>0.4100247025489807</v>
+        <v>0.4135356545448303</v>
       </c>
       <c r="J156" t="n">
         <v>3</v>
@@ -6731,7 +6731,7 @@
         <v>17.25</v>
       </c>
       <c r="L156" t="n">
-        <v>0.5276075601577759</v>
+        <v>0.5617133975028992</v>
       </c>
       <c r="M156" t="n">
         <v>5</v>
@@ -6754,7 +6754,7 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>0.7657504081726074</v>
+        <v>0.7256748676300049</v>
       </c>
       <c r="J157" t="n">
         <v>3</v>
@@ -6763,7 +6763,7 @@
         <v>18</v>
       </c>
       <c r="L157" t="n">
-        <v>0.5659937262535095</v>
+        <v>0.6253771781921387</v>
       </c>
       <c r="M157" t="n">
         <v>5</v>
@@ -6786,7 +6786,7 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>0.7370507717132568</v>
+        <v>0.7193089723587036</v>
       </c>
       <c r="J158" t="n">
         <v>3</v>
@@ -6795,7 +6795,7 @@
         <v>21</v>
       </c>
       <c r="L158" t="n">
-        <v>0.6125612258911133</v>
+        <v>0.5838305950164795</v>
       </c>
       <c r="M158" t="n">
         <v>5</v>
@@ -6816,7 +6816,7 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>0.7387571930885315</v>
+        <v>0.7381123900413513</v>
       </c>
       <c r="J159" t="n">
         <v>3</v>
@@ -6825,7 +6825,7 @@
         <v>27</v>
       </c>
       <c r="L159" t="n">
-        <v>0.5465166568756104</v>
+        <v>0.5090166330337524</v>
       </c>
       <c r="M159" t="n">
         <v>5</v>
@@ -6848,7 +6848,7 @@
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>0.5683902502059937</v>
+        <v>0.5698118209838867</v>
       </c>
       <c r="J160" t="n">
         <v>3</v>
@@ -6857,7 +6857,7 @@
         <v>26.75</v>
       </c>
       <c r="L160" t="n">
-        <v>0.5845332741737366</v>
+        <v>0.5925546884536743</v>
       </c>
       <c r="M160" t="n">
         <v>5</v>
@@ -6880,7 +6880,7 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>0.6053073406219482</v>
+        <v>0.7005208730697632</v>
       </c>
       <c r="J161" t="n">
         <v>3</v>
@@ -6889,7 +6889,7 @@
         <v>28.25</v>
       </c>
       <c r="L161" t="n">
-        <v>0.7292897701263428</v>
+        <v>0.7262193560600281</v>
       </c>
       <c r="M161" t="n">
         <v>5</v>
@@ -6912,7 +6912,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>0.5750089883804321</v>
+        <v>0.5780348181724548</v>
       </c>
       <c r="J162" t="n">
         <v>3</v>
@@ -6921,7 +6921,7 @@
         <v>17.25</v>
       </c>
       <c r="L162" t="n">
-        <v>0.6539128422737122</v>
+        <v>0.6658246517181396</v>
       </c>
       <c r="M162" t="n">
         <v>5</v>
@@ -6944,7 +6944,7 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>0.7747526168823242</v>
+        <v>0.7963777780532837</v>
       </c>
       <c r="J163" t="n">
         <v>3</v>
@@ -6953,7 +6953,7 @@
         <v>22</v>
       </c>
       <c r="L163" t="n">
-        <v>0.5942062735557556</v>
+        <v>0.6140480041503906</v>
       </c>
       <c r="M163" t="n">
         <v>5</v>
@@ -6974,7 +6974,7 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>0.6168196797370911</v>
+        <v>0.624757707118988</v>
       </c>
       <c r="J164" t="n">
         <v>3</v>
@@ -6983,7 +6983,7 @@
         <v>25.75</v>
       </c>
       <c r="L164" t="n">
-        <v>0.7462916374206543</v>
+        <v>0.7420055270195007</v>
       </c>
       <c r="M164" t="n">
         <v>5</v>
@@ -7006,7 +7006,7 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>0.7842923402786255</v>
+        <v>0.7855231165885925</v>
       </c>
       <c r="J165" t="n">
         <v>3</v>
@@ -7015,7 +7015,7 @@
         <v>35.25</v>
       </c>
       <c r="L165" t="n">
-        <v>0.6451925039291382</v>
+        <v>0.6934144496917725</v>
       </c>
       <c r="M165" t="n">
         <v>5</v>
@@ -7038,7 +7038,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>0.6339395046234131</v>
+        <v>0.6259607076644897</v>
       </c>
       <c r="J166" t="n">
         <v>3</v>
@@ -7047,7 +7047,7 @@
         <v>23.5</v>
       </c>
       <c r="L166" t="n">
-        <v>0.7011338472366333</v>
+        <v>0.6484429836273193</v>
       </c>
       <c r="M166" t="n">
         <v>5</v>
@@ -7070,7 +7070,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>0.6285346150398254</v>
+        <v>0.652283787727356</v>
       </c>
       <c r="J167" t="n">
         <v>3</v>
@@ -7079,7 +7079,7 @@
         <v>19.5</v>
       </c>
       <c r="L167" t="n">
-        <v>0.7199323177337646</v>
+        <v>0.7161546945571899</v>
       </c>
       <c r="M167" t="n">
         <v>5</v>
@@ -7102,7 +7102,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>0.7429258823394775</v>
+        <v>0.7586150169372559</v>
       </c>
       <c r="J168" t="n">
         <v>3</v>
@@ -7111,7 +7111,7 @@
         <v>20.5</v>
       </c>
       <c r="L168" t="n">
-        <v>0.7576414942741394</v>
+        <v>0.7419058084487915</v>
       </c>
       <c r="M168" t="n">
         <v>5</v>
@@ -7132,7 +7132,7 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="n">
-        <v>0.6880726218223572</v>
+        <v>0.6784882545471191</v>
       </c>
       <c r="J169" t="n">
         <v>3</v>
@@ -7141,7 +7141,7 @@
         <v>15.5</v>
       </c>
       <c r="L169" t="n">
-        <v>0.7000515460968018</v>
+        <v>0.7090731859207153</v>
       </c>
       <c r="M169" t="n">
         <v>5</v>
@@ -7164,7 +7164,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>0.6354477405548096</v>
+        <v>0.6380476951599121</v>
       </c>
       <c r="J170" t="n">
         <v>3</v>
@@ -7173,7 +7173,7 @@
         <v>28</v>
       </c>
       <c r="L170" t="n">
-        <v>0.7188889384269714</v>
+        <v>0.7053910493850708</v>
       </c>
       <c r="M170" t="n">
         <v>5</v>
@@ -7196,7 +7196,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>0.7252143621444702</v>
+        <v>0.7333022952079773</v>
       </c>
       <c r="J171" t="n">
         <v>3</v>
@@ -7205,7 +7205,7 @@
         <v>29.75</v>
       </c>
       <c r="L171" t="n">
-        <v>0.6383742690086365</v>
+        <v>0.6588344573974609</v>
       </c>
       <c r="M171" t="n">
         <v>5</v>
@@ -7228,7 +7228,7 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>0.6578299999237061</v>
+        <v>0.6523642539978027</v>
       </c>
       <c r="J172" t="n">
         <v>3</v>
@@ -7237,7 +7237,7 @@
         <v>24.25</v>
       </c>
       <c r="L172" t="n">
-        <v>0.6624307632446289</v>
+        <v>0.6300244331359863</v>
       </c>
       <c r="M172" t="n">
         <v>5</v>
@@ -7260,7 +7260,7 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>0.7707988619804382</v>
+        <v>0.6717712879180908</v>
       </c>
       <c r="J173" t="n">
         <v>3</v>
@@ -7269,7 +7269,7 @@
         <v>24.75</v>
       </c>
       <c r="L173" t="n">
-        <v>0.7269974946975708</v>
+        <v>0.6993997097015381</v>
       </c>
       <c r="M173" t="n">
         <v>5</v>
@@ -7290,7 +7290,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>0.7792378067970276</v>
+        <v>0.7581943273544312</v>
       </c>
       <c r="J174" t="n">
         <v>3</v>
@@ -7299,7 +7299,7 @@
         <v>20.25</v>
       </c>
       <c r="L174" t="n">
-        <v>0.7008092403411865</v>
+        <v>0.6920110583305359</v>
       </c>
       <c r="M174" t="n">
         <v>5</v>
@@ -7320,7 +7320,7 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>0.7544870376586914</v>
+        <v>0.7384237051010132</v>
       </c>
       <c r="J175" t="n">
         <v>3</v>
@@ -7329,7 +7329,7 @@
         <v>23.75</v>
       </c>
       <c r="L175" t="n">
-        <v>0.685026228427887</v>
+        <v>0.6886729001998901</v>
       </c>
       <c r="M175" t="n">
         <v>5</v>
@@ -7352,7 +7352,7 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>0.6544265151023865</v>
+        <v>0.6496595144271851</v>
       </c>
       <c r="J176" t="n">
         <v>3</v>
@@ -7361,7 +7361,7 @@
         <v>33</v>
       </c>
       <c r="L176" t="n">
-        <v>0.7712557315826416</v>
+        <v>0.7611434459686279</v>
       </c>
       <c r="M176" t="n">
         <v>5</v>
@@ -7384,7 +7384,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>0.832099974155426</v>
+        <v>0.8401345014572144</v>
       </c>
       <c r="J177" t="n">
         <v>3</v>
@@ -7393,7 +7393,7 @@
         <v>21</v>
       </c>
       <c r="L177" t="n">
-        <v>0.6921529173851013</v>
+        <v>0.6895379424095154</v>
       </c>
       <c r="M177" t="n">
         <v>5</v>
@@ -7416,7 +7416,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>0.8597308397293091</v>
+        <v>0.853410005569458</v>
       </c>
       <c r="J178" t="n">
         <v>3</v>
@@ -7425,7 +7425,7 @@
         <v>27.5</v>
       </c>
       <c r="L178" t="n">
-        <v>0.7789645195007324</v>
+        <v>0.7655214071273804</v>
       </c>
       <c r="M178" t="n">
         <v>5</v>
@@ -7448,7 +7448,7 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="n">
-        <v>0.7743117213249207</v>
+        <v>0.7871817350387573</v>
       </c>
       <c r="J179" t="n">
         <v>3</v>
@@ -7457,7 +7457,7 @@
         <v>31</v>
       </c>
       <c r="L179" t="n">
-        <v>0.8238269090652466</v>
+        <v>0.8059151172637939</v>
       </c>
       <c r="M179" t="n">
         <v>5</v>
